--- a/Result/checksun_type/裁剪加工.xlsx
+++ b/Result/checksun_type/裁剪加工.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>18.26</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>18.98</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>19.76</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>18.98</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>19.76</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>4912.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>2363.0</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>2363</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>2941.0</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>3073.38</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>3073.38</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-4.424937580884034</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>4912</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>4912.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>18.06</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>19.03</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>19.79</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>19.03</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>19.79</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>1840.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>1864.8</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>1864.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>3067.5</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>3155.06</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>3155.06</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-217.4550994128708</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>1840</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>1840.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>18.01</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>19.1</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>19.83</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>19.83</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>834.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>2456.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>2456</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>3119.4</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>3233.6</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>3233.6</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-184.8747913366778</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>834</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>834.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>18.1</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>19.2</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>19.89</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>19.89</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>3206.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>3279.8</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>3279.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>3621.8</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>3382.56</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>3382.56</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-23.94310868009234</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>3206</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>3206.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>18.3</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>19.3</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>19.95</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>19.95</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>1023.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>3059.2</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>3059.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>3382.8</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>3397.58</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>3397.58</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-47.32845100353916</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>1023</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>1023.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>18.48</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>19.41</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>20.02</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>19.41</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>20.02</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>2421.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>3519.0</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>3519</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>3523.9</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>3440.96</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>3440.96</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>154.8470760702357</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>2421</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>2421.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>18.74</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>19.52</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>20.09</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>19.52</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>20.09</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>4796.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>4270.2</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>4270.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>3430.5</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>3474.84</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>3474.84</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>288.3532906016908</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>4796</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>4796.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>18.96</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>19.61</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>20.15</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>19.61</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>20.15</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>4953.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>3782.8</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>3782.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>3139.9</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>4095.92</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>4095.92</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>214.3138366965663</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>4953</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>4953.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>19.09</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>19.7</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>20.2</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>20.2</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>2103.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>3963.8</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>3963.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>2759.8</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>4086.18</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>4086.18</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>84.06769409294066</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>2103</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>2103.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>19.24</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>19.77</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>20.25</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>19.77</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>20.25</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>3322.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>3706.4</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>3706.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>2607.3</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>4188.2</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>4188.2</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>200.3565012987274</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>3322</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>3322.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>19.42</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>19.83</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>20.31</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>19.83</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>20.31</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>6177.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>3528.8</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>3528.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>2407.1</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>4181.94</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>4181.94</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>228.7206365463248</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>6177</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>6177.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>10.048</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>10.43</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>10.48</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>10.48</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>1209.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>941.4</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>941.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>1307.1</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>2381.9</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>2381.9</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-218.2408367358291</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>1209</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>1209.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>10.038</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>10.47</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>10.48</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>10.48</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>650.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>1207.0</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>1207</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>1310.1</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>2426.9</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>2426.9</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-245.0105990605005</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>650</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>650.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>10.078</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>10.52</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>10.48</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>10.52</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>10.48</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>845.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>1391.8</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>1391.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>1576.2</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>2454.74</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>2454.74</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-214.6098809864416</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>845</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>845.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>10.138</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>10.57</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>10.49</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>10.49</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>1053.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>1602.2</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>1602.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>1633.5</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>2481.04</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>2481.04</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-184.4085022739844</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>1053</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>1053.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>10.2</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>10.62</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>10.49</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>10.49</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>950.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>1586.0</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>1586</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>1665.5</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>2491.66</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>2491.66</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-156.9633718892605</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>950</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>950.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>10.28</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>10.66</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>10.66</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>10.5</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>2537.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>1672.8</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>1672.8</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>1698.0</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>2587.24</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>2587.24</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-101.1144937721815</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>2537</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>2537.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>10.34</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>10.71</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>10.71</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>10.5</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>1574.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>1413.2</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>1413.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>1605.3</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>2589.52</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>2589.52</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-187.7548645416337</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>1574</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>1574.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>10.35</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>10.74</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>10.49</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>10.74</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>10.49</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>1897.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>1760.6</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>1760.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>1771.3</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>2578.42</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>2578.42</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-201.6427204786496</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>1897</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>1897.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>10.39</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>10.76</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>10.49</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>10.76</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>10.49</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>972.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>1664.8</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>1664.8</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>1733.5</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>2593.66</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>2593.66</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-248.8881318001493</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>972</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>972.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>10.46</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>10.77</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>10.48</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>10.77</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>10.48</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>1384.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>1745.0</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>1745</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>1796.2</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>2627.8</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>2627.8</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-208.3855718380007</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>1384</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>1384.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>10.51</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>10.77</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>10.48</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>10.77</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>10.48</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>1239.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>1723.2</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>1723.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>1847.8</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>2657.88</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>2657.88</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-187.225287183574</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>1239</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>1239.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>價_量;【c】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>19.69</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>17.01</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>13.06</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>17.01</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>13.06</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>1030.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>2356.0</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>2356</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>2480.9</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>915.86</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>915.86</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>119.6203873874458</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>1030</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>1030.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>20.04</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>16.53</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>12.87</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>16.53</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>12.87</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>580.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>3385.4</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>3385.4</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>2584.3</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>942.8</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>942.8</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>245.8964964244842</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>580</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>580.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>20.87</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>16.11</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>12.72</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>16.11</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>12.72</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>1513.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>3764.8</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>3764.8</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>2563.1</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>948.5</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>948.5</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>465.7232058908075</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>1513</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>1513.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>21.44</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>15.68</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>12.57</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>15.68</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>12.57</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>3277.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>3810.0</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>3810</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>2487.1</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>936.3</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>936.3</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>663.1641049180262</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>3277</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>3277.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>21.61</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>15.22</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>12.41</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>15.22</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>12.41</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>5380.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>3492.6</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>3492.6</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>2168.5</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>875.2</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>875.2</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>732.5380997812654</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>5380</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>5380.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>22.02</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>14.69</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>12.23</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>14.69</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>12.23</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>6177.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>2605.8</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>2605.8</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>1666.2</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>777.32</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>777.3200000000001</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>580.1603031651334</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>6177</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>6177.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>22.41</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>14.1</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>12.02</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>12.02</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>2477.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>1783.2</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>1783.2</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>1153.7</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>667.98</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>667.98</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>256.3648686004763</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>2477</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>2477.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>23.03</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>13.46</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>11.78</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>13.46</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>11.78</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>1739.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>1361.4</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>1361.4</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>988.7</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>628.3</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>628.3</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>181.0726453438062</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>1739</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>1739.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>20.67</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>12.85</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>11.57</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>12.85</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>11.57</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>1690.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>1164.2</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>1164.2</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>880.0</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>599.74</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>599.74</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>146.1168747862846</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>1690</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>1690.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>18.56</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>12.34</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>11.4</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>12.34</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>11.4</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>946.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>844.4</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>844.4</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>769.8</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>568.28</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>568.28</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>96.21159989031503</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>946</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>946.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>16.08</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>11.72</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>11.19</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>11.72</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>11.19</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>2064.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>726.6</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>726.6</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>730.6</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>554.88</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>554.88</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>101.1965071857043</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>2064</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>2064.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>15.8</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>15.52</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>15.23</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>15.52</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>15.23</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>4593505.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>2680780.4</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>2680780.4</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>3764386.6</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>2627573.92</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>2627573.92</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>101307.1362508028</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>4593505</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>4593505.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>15.73</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>15.48</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>15.2</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>15.48</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>15.2</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>1727966.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>2288603.4</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>2288603.4</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>3629902.4</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>2660960.7</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>2660960.7</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-40678.14108390221</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>1727966</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>1727966.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,21 +16107,17 @@
           <t>15.74</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>15.46</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
+      <c r="AM37" t="n">
+        <v>15.46</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>15.18</v>
+      </c>
+      <c r="AO37" t="inlineStr">
         <is>
           <t>15.18</t>
         </is>
       </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>15.18</t>
-        </is>
-      </c>
       <c r="AP37" t="inlineStr">
         <is>
           <t>19.50</t>
@@ -16372,20 +16158,16 @@
           <t>1459310.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>2870687.4</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>2870687.4</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>3597279.3</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>2694695.38</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>2694695.38</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>64960.57490522927</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>1459310</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>1459310.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,21 +16537,17 @@
           <t>15.78</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>15.44</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
+      <c r="AM38" t="n">
+        <v>15.44</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>15.17</v>
+      </c>
+      <c r="AO38" t="inlineStr">
         <is>
           <t>15.17</t>
         </is>
       </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>15.17</t>
-        </is>
-      </c>
       <c r="AP38" t="inlineStr">
         <is>
           <t>24.75</t>
@@ -16808,20 +16588,16 @@
           <t>3051011.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>3980280.0</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>3980280</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>3565283.9</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>2749809.62</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>2749809.62</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>242337.5772145167</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>3051011</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>3051011.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,21 +16967,17 @@
           <t>15.84</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>15.44</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
+      <c r="AM39" t="n">
+        <v>15.44</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>15.16</v>
+      </c>
+      <c r="AO39" t="inlineStr">
         <is>
           <t>15.16</t>
         </is>
       </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>15.16</t>
-        </is>
-      </c>
       <c r="AP39" t="inlineStr">
         <is>
           <t>42.98</t>
@@ -17244,20 +17018,16 @@
           <t>2572110.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>4827581.8</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>4827581.8</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>3398051.1</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>2801800.0</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>2801800</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>316538.9884701231</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>2572110</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>2572110.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,21 +17397,17 @@
           <t>15.78</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>15.42</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
+      <c r="AM40" t="n">
+        <v>15.42</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>15.15</v>
+      </c>
+      <c r="AO40" t="inlineStr">
         <is>
           <t>15.15</t>
         </is>
       </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>15.15</t>
-        </is>
-      </c>
       <c r="AP40" t="inlineStr">
         <is>
           <t>47.65</t>
@@ -17680,20 +17448,16 @@
           <t>2632620.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>4847992.8</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>4847992.8</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>3291715.8</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>2772684.66</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>2772684.66</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>462546.8621041994</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>2632620</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>2632620.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,21 +17827,17 @@
           <t>15.72</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>15.4</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
+      <c r="AM41" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>15.14</v>
+      </c>
+      <c r="AO41" t="inlineStr">
         <is>
           <t>15.14</t>
         </is>
       </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>15.14</t>
-        </is>
-      </c>
       <c r="AP41" t="inlineStr">
         <is>
           <t>69.25</t>
@@ -18116,20 +17878,16 @@
           <t>4638386.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>4971201.4</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>4971201.4</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>3166508.6</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>2769611.28</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>2769611.28</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>648126.7936491584</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>4638386</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>4638386.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>15.57</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>15.37</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>15.12</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>15.37</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>15.12</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>7007273.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>4323871.2</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>4323871.2</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>2943997.3</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>2695658.54</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>2695658.54</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>675190.0960830585</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>7007273</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>7007273.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>15.4</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>15.34</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>15.1</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>15.34</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>15.1</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>7287520.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>3150287.8</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>3150287.8</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>2427579.6</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>2584239.14</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>2584239.14</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>435928.7032713783</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>7287520</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>7287520.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>15.25</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>15.32</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>15.09</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>15.32</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>15.09</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>2674165.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>1968520.4</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>1968520.4</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>1838211.0</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>2483315.54</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>2483315.54</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>48531.36699500051</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>2674165</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>2674165.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>15.19</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>15.3</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>15.08</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>15.08</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>3248663.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>1735438.8</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>1735438.8</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>1739755.6</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>2467738.26</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>2467738.26</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-12338.62650678935</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>3248663</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>3248663.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>19.75</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>19.32</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>19.6</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>19.32</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>19.6</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>132621113.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>46668688.8</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>46668688.8</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>37930663.3</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>24467742.9</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>24467742.9</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>9216793.900870845</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>132621113</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>132621113.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>19.41</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>19.27</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>19.58</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>19.27</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>19.58</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>26830670.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>25226666.0</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>25226666</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>26250725.0</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>22382197.58</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>22382197.58</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>1377500.007797588</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>26830670</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>26830670.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>19.28</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>19.26</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>19.58</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>19.26</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>19.58</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>43465545.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>24261943.4</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>24261943.4</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>24604465.6</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>22403454.84</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>22403454.84</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>1464002.624557309</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>43465545</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>43465545.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>19.29</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>19.27</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>19.58</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>19.27</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>19.58</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>14439758.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>23879779.4</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>23879779.4</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>21672869.3</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>21839201.36</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>21839201.36</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-247016.0523772761</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>14439758</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>14439758.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>19.43</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>19.31</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>19.6</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>19.31</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>19.6</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>15986358.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>26971384.2</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>26971384.2</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>21268337.4</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>21836585.24</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>21836585.24</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>427399.3038724996</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>15986358</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>15986358.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>19.49</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>19.35</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>19.61</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>19.61</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>25410999.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>29192637.8</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>29192637.8</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>20825724.3</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>21906077.96</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>21906077.96</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>1209878.409091018</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>25410999</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>25410999.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>19.56</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>19.4</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>19.63</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>19.63</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>22007057.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>27274784.0</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>27274784</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>19852251.1</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>21873902.02</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>21873902.02</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>1274712.794792797</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>22007057</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>22007057.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>19.46</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>19.42</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>19.63</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>19.42</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>19.63</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>41554725.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>24946987.8</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>24946987.8</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>20320292.3</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>22642043.72</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>22642043.72</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>1686515.96026703</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>41554725</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>41554725.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>19.25</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>19.44</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>19.64</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>19.44</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>19.64</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>29897782.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>19465959.2</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>19465959.2</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>19736315.2</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>22577403.58</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>22577403.58</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>120180.4837921113</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>29897782</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>29897782.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>19.11</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>19.45</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>19.65</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>19.45</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>19.65</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>27092626.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>15565290.6</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>15565290.6</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>18973182.0</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>22772553.22</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>22772553.22</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-872775.6070217751</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>27092626</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>27092626.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>18.98</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>19.46</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>19.67</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>19.46</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>19.67</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>15821730.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>12458810.8</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>12458810.8</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>18276539.7</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>22770756.54</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>22770756.54</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>-1959561.322219411</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>15821730</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>15821730.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>13.93</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>13.95</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>14.38</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>14.38</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>12337786.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>4346256.0</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>4346256</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>3094679.9</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>2830564.88</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>2830564.88</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>884033.7207037453</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>12337786</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>12337786.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>13.82</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>13.94</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>14.39</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>13.94</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>14.39</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>2074810.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>2260604.8</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>2260604.8</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>2001986.7</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>2701788.18</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>2701788.18</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>144599.2477593212</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>2074810</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>2074810.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>13.78</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>13.96</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>14.41</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>13.96</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>14.41</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>5665814.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>2182046.2</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>2182046.2</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>1937507.8</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>2797235.68</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>2797235.68</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>182704.5989901694</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>5665814</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>5665814.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>13.73</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>13.98</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>14.44</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>13.98</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>14.44</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>851621.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>1349338.0</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>1349338</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>1601781.0</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>2720066.3</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>2720066.3</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>-154134.7777868395</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>851621</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>851621.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>13.81</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>14.03</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>14.47</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>14.03</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>14.47</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>801249.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>1718868.8</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>1718868.8</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>1622388.2</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>2787341.68</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>2787341.68</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>-114022.6811187507</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>801249</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>801249.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>13.87</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>14.07</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>14.5</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>14.5</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>1909530.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>1843103.8</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>1843103.8</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>1766043.4</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>2813031.08</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>2813031.08</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>-47250.44726723991</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>1909530</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>1909530.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>13.93</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>14.11</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>14.52</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>14.11</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>14.52</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>1682017.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>1743368.6</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>1743368.6</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>1710099.1</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>2833070.44</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>2833070.44</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>-68918.41864839452</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>1682017</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>1682017.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>13.95</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>14.16</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>14.54</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>14.16</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>14.54</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>1502273.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>1692969.4</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>1692969.4</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>1686360.5</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>2843848.22</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>2843848.22</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>-73034.89852688694</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>1502273</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>1502273.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>13.98</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>14.2</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>14.56</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>14.56</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>2699275.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>1854224.0</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>1854224</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>1615402.6</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>2881080.16</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>2881080.16</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>-57048.9091202016</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>2699275</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>2699275.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>14.0</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>14.24</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>14.58</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>14.24</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>14.58</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>1422424.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>1525907.6</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>1525907.6</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>1578559.3</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>2917090.52</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>2917090.52</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>-160424.5346420724</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>1422424</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>1422424.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>13.99</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>14.27</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>14.6</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>14.27</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>14.6</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>1410854.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>1688983.0</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>1688983</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>1547892.3</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>2999483.74</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>2999483.74</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>-165569.0877218139</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>1410854</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>1410854.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>37.47</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>38.08</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>40.03</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>38.08</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>40.03</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>35810040.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>75499582.6</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>75499582.59999999</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>55792550.2</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>33454972.78</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>33454972.78</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>7886638.29228013</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>35810040</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>35810040.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>36.87</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>38.11</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>40.07</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>38.11</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>40.07</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>39561838.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>77102277.8</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>77102277.8</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>54515793.2</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>33864219.92</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>33864219.92</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>11730479.54280426</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>39561838</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>39561838.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>36.60000000000001</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>38.22</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>40.17</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>38.22</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>40.17</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>232650449.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>74142370.0</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>74142370</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>57245793.0</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>34130931.06</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>34130931.06</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>16400757.27416717</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>232650449</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>232650449.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>36.61</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>38.41</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>40.3</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>38.41</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>40.3</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>41298962.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>35487232.0</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>35487232</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>35914543.8</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>29950115.64</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>29950115.64</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>1798775.809179619</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>41298962</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>41298962.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>36.73</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>40.43</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>40.43</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>28176624.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>37871124.0</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>37871124</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>34509118.0</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>29545425.32</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>29545425.32</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>1376505.330298137</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>28176624</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>28176624.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>37.07000000000001</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>38.8</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>40.58</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>40.58</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>43823516.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>36085517.8</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>36085517.8</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>35025550.9</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>29409986.0</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>29409986</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>2130065.670099653</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>43823516</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>43823516.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>37.47000000000001</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>39.02</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>40.75</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>39.02</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>40.75</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>24762299.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>31929308.6</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>31929308.6</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>32595150.7</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>29130934.74</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>29130934.74</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>1454053.953026839</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>24762299</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>24762299.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>37.65000000000001</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>39.23</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>40.9</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>39.23</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>40.9</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>39374759.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>40349216.0</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>40349216</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>31454761.9</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>29061426.18</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>29061426.18</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>2478665.680314712</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>39374759</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>39374759.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>37.99</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>39.42</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>41.05</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>39.42</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>41.05</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>53218422.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>36341855.6</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>36341855.6</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>29562657.9</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>28846965.04</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>28846965.04</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>2288252.230714723</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>53218422</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>53218422.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>38.31</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>39.58</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>41.17</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>39.58</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>41.17</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>19248593.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>31147112.0</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>31147112</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>25871081.1</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>28091032.78</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>28091032.78</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>451260.1159035005</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>19248593</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>19248593.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>38.46</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>39.69</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>41.29</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>39.69</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>41.29</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>23042470.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>33965584.0</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>33965584</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>26178217.9</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>28206383.42</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>28206383.42</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>1450493.769176625</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>23042470</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>23042470.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34445,7 +33983,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34629,15 +34167,11 @@
           <t>20.02</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>19.78</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>19.94</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>19.78</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>19.94</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34684,20 +34218,16 @@
           <t>26219629.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>16889576.0</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>16889576</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>17236189.3</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>20277790.28</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>20277790.28</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34244,10 @@
           <t>-302881.9023336619</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>26219629</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>26219629.0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
@@ -34881,7 +34413,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -35065,15 +34597,11 @@
           <t>19.89</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>19.73</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>19.94</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>19.73</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>19.94</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -35120,20 +34648,16 @@
           <t>17532722.0</t>
         </is>
       </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>14859100.0</t>
-        </is>
+      <c r="AX80" t="n">
+        <v>14859100</v>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>16642108.4</t>
         </is>
       </c>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>20371841.18</t>
-        </is>
+      <c r="AZ80" t="n">
+        <v>20371841.18</v>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
@@ -35150,8 +34674,10 @@
           <t>-1128834.726736229</t>
         </is>
       </c>
-      <c r="BD80" t="n">
-        <v>17532722</v>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>17532722.0</t>
+        </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
@@ -35317,7 +34843,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -35501,15 +35027,11 @@
           <t>19.84</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>19.69</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>19.95</t>
-        </is>
+      <c r="AM81" t="n">
+        <v>19.69</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>19.95</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -35556,20 +35078,16 @@
           <t>11740057.0</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>16014559.2</t>
-        </is>
+      <c r="AX81" t="n">
+        <v>16014559.2</v>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
           <t>16278001.2</t>
         </is>
       </c>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>20292426.12</t>
-        </is>
+      <c r="AZ81" t="n">
+        <v>20292426.12</v>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
@@ -35586,8 +35104,10 @@
           <t>-1337711.771356456</t>
         </is>
       </c>
-      <c r="BD81" t="n">
-        <v>11740057</v>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>11740057.0</t>
+        </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
@@ -35753,7 +35273,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -35937,15 +35457,11 @@
           <t>19.82</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>19.67</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>19.96</t>
-        </is>
+      <c r="AM82" t="n">
+        <v>19.67</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>19.96</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -35992,20 +35508,16 @@
           <t>18789662.0</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>18102005.0</t>
-        </is>
+      <c r="AX82" t="n">
+        <v>18102005</v>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
           <t>17635266.7</t>
         </is>
       </c>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>20278770.0</t>
-        </is>
+      <c r="AZ82" t="n">
+        <v>20278770</v>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
@@ -36022,8 +35534,10 @@
           <t>-967689.4504083358</t>
         </is>
       </c>
-      <c r="BD82" t="n">
-        <v>18789662</v>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>18789662.0</t>
+        </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
@@ -36189,7 +35703,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -36373,15 +35887,11 @@
           <t>19.89</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>19.66</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>19.97</t>
-        </is>
+      <c r="AM83" t="n">
+        <v>19.66</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>19.97</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -36428,20 +35938,16 @@
           <t>10165810.0</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>17346115.8</t>
-        </is>
+      <c r="AX83" t="n">
+        <v>17346115.8</v>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
           <t>24061820.1</t>
         </is>
       </c>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>20181907.52</t>
-        </is>
+      <c r="AZ83" t="n">
+        <v>20181907.52</v>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
@@ -36458,8 +35964,10 @@
           <t>-1159840.618682154</t>
         </is>
       </c>
-      <c r="BD83" t="n">
-        <v>10165810</v>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>10165810.0</t>
+        </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
@@ -36625,7 +36133,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -36809,15 +36317,11 @@
           <t>19.94</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>19.65</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>19.97</t>
-        </is>
+      <c r="AM84" t="n">
+        <v>19.65</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>19.97</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -36864,20 +36368,16 @@
           <t>16067249.0</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>17582802.6</t>
-        </is>
+      <c r="AX84" t="n">
+        <v>17582802.6</v>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
           <t>24285645.8</t>
         </is>
       </c>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>20299032.42</t>
-        </is>
+      <c r="AZ84" t="n">
+        <v>20299032.42</v>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
@@ -36894,8 +36394,10 @@
           <t>-468935.2655489594</t>
         </is>
       </c>
-      <c r="BD84" t="n">
-        <v>16067249</v>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>16067249.0</t>
+        </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -37061,7 +36563,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -37245,15 +36747,11 @@
           <t>20.06</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>19.64</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>19.99</t>
-        </is>
+      <c r="AM85" t="n">
+        <v>19.64</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>19.99</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -37300,20 +36798,16 @@
           <t>23310018.0</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>18425116.8</t>
-        </is>
+      <c r="AX85" t="n">
+        <v>18425116.8</v>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
           <t>24110880.8</t>
         </is>
       </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>20453854.52</t>
-        </is>
+      <c r="AZ85" t="n">
+        <v>20453854.52</v>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
@@ -37330,8 +36824,10 @@
           <t>-97476.96587479487</t>
         </is>
       </c>
-      <c r="BD85" t="n">
-        <v>23310018</v>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>23310018.0</t>
+        </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
@@ -37497,7 +36993,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -37681,15 +37177,11 @@
           <t>20.1</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>19.62</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
+      <c r="AM86" t="n">
+        <v>19.62</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>20</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -37736,20 +37228,16 @@
           <t>22177286.0</t>
         </is>
       </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>16541443.2</t>
-        </is>
+      <c r="AX86" t="n">
+        <v>16541443.2</v>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
           <t>23454311.7</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>20348159.38</t>
-        </is>
+      <c r="AZ86" t="n">
+        <v>20348159.38</v>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
@@ -37766,8 +37254,10 @@
           <t>-339351.8961304575</t>
         </is>
       </c>
-      <c r="BD86" t="n">
-        <v>22177286</v>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>22177286.0</t>
+        </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
@@ -37933,7 +37423,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -38117,15 +37607,11 @@
           <t>20.13</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>19.6</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
+      <c r="AM87" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>20</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -38172,20 +37658,16 @@
           <t>15010216.0</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>17168528.4</t>
-        </is>
+      <c r="AX87" t="n">
+        <v>17168528.4</v>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
           <t>22516228.9</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>20143353.8</t>
-        </is>
+      <c r="AZ87" t="n">
+        <v>20143353.8</v>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
@@ -38202,8 +37684,10 @@
           <t>-551403.6573481709</t>
         </is>
       </c>
-      <c r="BD87" t="n">
-        <v>15010216</v>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>15010216.0</t>
+        </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
@@ -38369,7 +37853,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -38553,15 +38037,11 @@
           <t>20.17</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>19.57</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>20.01</t>
-        </is>
+      <c r="AM88" t="n">
+        <v>19.57</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>20.01</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -38608,20 +38088,16 @@
           <t>11349244.0</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>30777524.4</t>
-        </is>
+      <c r="AX88" t="n">
+        <v>30777524.4</v>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>22335947.5</t>
         </is>
       </c>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>20370385.8</t>
-        </is>
+      <c r="AZ88" t="n">
+        <v>20370385.8</v>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
@@ -38638,8 +38114,10 @@
           <t>-66741.39989675581</t>
         </is>
       </c>
-      <c r="BD88" t="n">
-        <v>11349244</v>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>11349244.0</t>
+        </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
@@ -38805,7 +38283,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -38989,15 +38467,11 @@
           <t>20.05</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>19.55</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>20.02</t>
-        </is>
+      <c r="AM89" t="n">
+        <v>19.55</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>20.02</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -39044,20 +38518,16 @@
           <t>20278820.0</t>
         </is>
       </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>30988489.0</t>
-        </is>
+      <c r="AX89" t="n">
+        <v>30988489</v>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>22686745.2</t>
         </is>
       </c>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>20671912.34</t>
-        </is>
+      <c r="AZ89" t="n">
+        <v>20671912.34</v>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
@@ -39074,8 +38544,10 @@
           <t>1020263.875030149</t>
         </is>
       </c>
-      <c r="BD89" t="n">
-        <v>20278820</v>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>20278820.0</t>
+        </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>

--- a/Result/checksun_type/裁剪加工.xlsx
+++ b/Result/checksun_type/裁剪加工.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ78"/>
+  <dimension ref="A1:CJ89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28725,22 +28725,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>價_量;【b1】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>1237.222</t>
+          <t>325.91</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -28750,7 +28750,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -28765,12 +28765,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>-5.77</t>
+          <t>-28.68</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -28780,37 +28780,37 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2025-09-25 00:00:00</t>
+          <t>2025-08-15 00:00:00</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>2025-10-13 00:00:00</t>
+          <t>2025-08-26 00:00:00</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>2025-07-30 00:00:00</t>
+          <t>2025-03-10 00:00:00</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>2025-08-27 00:00:00</t>
+          <t>2025-03-12 00:00:00</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -28820,12 +28820,12 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -28835,12 +28835,12 @@
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-11.36</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-15.62</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr">
@@ -28850,12 +28850,12 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
@@ -28866,121 +28866,121 @@
       <c r="AC68" t="inlineStr"/>
       <c r="AD68" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE68" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>326</t>
         </is>
       </c>
       <c r="AF68" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG68" t="inlineStr">
         <is>
-          <t>85.93</t>
+          <t>57.58</t>
         </is>
       </c>
       <c r="AH68" t="n">
-        <v>0.63</v>
+        <v>-1.26</v>
       </c>
       <c r="AI68" t="n">
-        <v>1.62</v>
+        <v>2.09</v>
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AL68" t="inlineStr">
         <is>
-          <t>20.52</t>
+          <t>38.74</t>
         </is>
       </c>
       <c r="AM68" t="n">
-        <v>20.19</v>
+        <v>37.95</v>
       </c>
       <c r="AN68" t="n">
-        <v>19.99</v>
+        <v>39.48</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>20.27</t>
+          <t>40.93</t>
         </is>
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>35.99</t>
+          <t>59.95</t>
         </is>
       </c>
       <c r="AQ68" t="n">
-        <v>0.19</v>
+        <v>-0.14</v>
       </c>
       <c r="AR68" t="n">
-        <v>0.14</v>
+        <v>-0.35</v>
       </c>
       <c r="AS68" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr">
         <is>
-          <t>-82.27</t>
+          <t>-113.14</t>
         </is>
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
-          <t>29422182.78288543</t>
+          <t>148998047.268034</t>
         </is>
       </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>25460455.0</t>
+          <t>12502974.0</t>
         </is>
       </c>
       <c r="AX68" t="n">
-        <v>17184128.2</v>
+        <v>14661037.6</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
-          <t>18236884.7</t>
+          <t>20557419.7</t>
         </is>
       </c>
       <c r="AZ68" t="n">
-        <v>20624284.56</v>
+        <v>32207875.34</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>-1052756</t>
+          <t>-5896382</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
         <is>
-          <t>-505642.3241600473</t>
+          <t>-1246342.232336838</t>
         </is>
       </c>
       <c r="BC68" t="inlineStr">
         <is>
-          <t>-3892.7030364573</t>
+          <t>-5563232.276525833</t>
         </is>
       </c>
       <c r="BD68" t="inlineStr">
         <is>
-          <t>25460455.0</t>
+          <t>12502974.0</t>
         </is>
       </c>
       <c r="BE68" t="inlineStr">
@@ -28990,27 +28990,27 @@
       </c>
       <c r="BF68" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="BG68" t="inlineStr">
         <is>
-          <t>2025/12/01</t>
+          <t>2025/08/07</t>
         </is>
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-7.83</t>
         </is>
       </c>
       <c r="BI68" t="inlineStr">
         <is>
-          <t>春源</t>
+          <t>新光鋼</t>
         </is>
       </c>
       <c r="BJ68" t="inlineStr">
         <is>
-          <t>春源</t>
+          <t>新光鋼</t>
         </is>
       </c>
       <c r="BK68" t="inlineStr">
@@ -29025,62 +29025,62 @@
       </c>
       <c r="BM68" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BN68" t="inlineStr">
         <is>
-          <t>1.166589855613648</t>
+          <t>-13.67996844119094</t>
         </is>
       </c>
       <c r="BO68" t="inlineStr">
         <is>
-          <t>-1.196134907171803</t>
+          <t>-10.11024290164889</t>
         </is>
       </c>
       <c r="BP68" t="inlineStr">
         <is>
-          <t>3.290941182656901</t>
+          <t>24.12947661306339</t>
         </is>
       </c>
       <c r="BQ68" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR68" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS68" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT68" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.54</t>
         </is>
       </c>
       <c r="BU68" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="BV68" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>15.81</t>
         </is>
       </c>
       <c r="BW68" t="inlineStr">
         <is>
-          <t>10.84%</t>
+          <t>8.69%</t>
         </is>
       </c>
       <c r="BX68" t="inlineStr">
         <is>
-          <t>7.27%</t>
+          <t>5.19%</t>
         </is>
       </c>
       <c r="BY68" t="inlineStr">
@@ -29090,52 +29090,52 @@
       </c>
       <c r="BZ68" t="inlineStr">
         <is>
-          <t>13374</t>
+          <t>12284</t>
         </is>
       </c>
       <c r="CA68" t="inlineStr">
         <is>
-          <t>工程50.74%、鋼板35.82%、特殊鋼帶板4.32%、矽鋼材4.32%、特殊鋼材2.90%、倉儲設備1.15%、型鋼0.57%、加工業務0.18% (2024年)</t>
+          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
         </is>
       </c>
       <c r="CB68" t="inlineStr">
         <is>
-          <t>春源-鋼鐵工業-上市</t>
+          <t>新光鋼-鋼鐵工業-上市</t>
         </is>
       </c>
       <c r="CC68" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上上市</t>
+          <t>鋼鐵工業右下上市</t>
         </is>
       </c>
       <c r="CD68" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CE68" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CF68" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CG68" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="CH68" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>36.35</t>
         </is>
       </c>
       <c r="CI68" t="inlineStr">
         <is>
-          <t>** 鋼鐵 - 冷熱軋鋼板捲、棒鋼盤元(捲狀條鋼)、冷熱軋不鏽鋼板捲、不鏽鋼棒線、裁剪加工、金屬製品、模具、建築工程** 建材營造 - 結構工程</t>
+          <t>** 鋼鐵 - 裁剪加工** 建材營造 - 基礎工程、結構工程** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 鋼材、塔架、其他配件</t>
         </is>
       </c>
       <c r="CJ68" t="inlineStr">
@@ -29147,22 +29147,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>603.128</t>
+          <t>410.32</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -29172,7 +29172,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -29182,17 +29182,17 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>-10.01</t>
+          <t>-63.08</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -29202,37 +29202,37 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2025-09-25 00:00:00</t>
+          <t>2025-08-15 00:00:00</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>2025-10-13 00:00:00</t>
+          <t>2025-08-26 00:00:00</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>2025-07-30 00:00:00</t>
+          <t>2025-03-10 00:00:00</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>2025-08-27 00:00:00</t>
+          <t>2025-03-12 00:00:00</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -29242,12 +29242,12 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -29257,12 +29257,12 @@
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>-9.97</t>
         </is>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-15.62</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr">
@@ -29272,12 +29272,12 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12.62</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
@@ -29288,121 +29288,121 @@
       <c r="AC69" t="inlineStr"/>
       <c r="AD69" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE69" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>326</t>
         </is>
       </c>
       <c r="AF69" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG69" t="inlineStr">
         <is>
-          <t>85.93</t>
+          <t>84.98</t>
         </is>
       </c>
       <c r="AH69" t="n">
-        <v>-0.15</v>
+        <v>0</v>
       </c>
       <c r="AI69" t="n">
-        <v>1.56</v>
+        <v>2.32</v>
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-4.03</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AL69" t="inlineStr">
         <is>
-          <t>20.48</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="AM69" t="n">
-        <v>20.16</v>
+        <v>37.97</v>
       </c>
       <c r="AN69" t="n">
-        <v>19.98</v>
+        <v>39.56</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>20.27</t>
+          <t>40.98</t>
         </is>
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>38.09</t>
+          <t>68.34</t>
         </is>
       </c>
       <c r="AQ69" t="n">
-        <v>0.18</v>
+        <v>-0.13</v>
       </c>
       <c r="AR69" t="n">
-        <v>0.13</v>
+        <v>-0.41</v>
       </c>
       <c r="AS69" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr">
         <is>
-          <t>-83.86</t>
+          <t>-115.10</t>
         </is>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
-          <t>29422182.78288543</t>
+          <t>148998047.268034</t>
         </is>
       </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>12281215.0</t>
+          <t>15869530.0</t>
         </is>
       </c>
       <c r="AX69" t="n">
-        <v>15176666.8</v>
+        <v>15717891.6</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>16864844.9</t>
+          <t>42572167.2</t>
         </is>
       </c>
       <c r="AZ69" t="n">
-        <v>20327098.3</v>
+        <v>32421504.8</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>-1688178</t>
+          <t>-26854275</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
         <is>
-          <t>-596869.5280007</t>
+          <t>-461453.1333933839</t>
         </is>
       </c>
       <c r="BC69" t="inlineStr">
         <is>
-          <t>-777304.7251375262</t>
+          <t>-5227155.702291623</t>
         </is>
       </c>
       <c r="BD69" t="inlineStr">
         <is>
-          <t>12281215.0</t>
+          <t>15869530.0</t>
         </is>
       </c>
       <c r="BE69" t="inlineStr">
@@ -29412,27 +29412,27 @@
       </c>
       <c r="BF69" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="BG69" t="inlineStr">
         <is>
-          <t>2025/12/01</t>
+          <t>2025/08/07</t>
         </is>
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="BI69" t="inlineStr">
         <is>
-          <t>春源</t>
+          <t>新光鋼</t>
         </is>
       </c>
       <c r="BJ69" t="inlineStr">
         <is>
-          <t>春源</t>
+          <t>新光鋼</t>
         </is>
       </c>
       <c r="BK69" t="inlineStr">
@@ -29447,27 +29447,27 @@
       </c>
       <c r="BM69" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BN69" t="inlineStr">
         <is>
-          <t>1.166589855613648</t>
+          <t>-13.67996844119094</t>
         </is>
       </c>
       <c r="BO69" t="inlineStr">
         <is>
-          <t>-1.196134907171803</t>
+          <t>-10.11024290164889</t>
         </is>
       </c>
       <c r="BP69" t="inlineStr">
         <is>
-          <t>3.290941182656901</t>
+          <t>24.12947661306339</t>
         </is>
       </c>
       <c r="BQ69" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR69" t="inlineStr">
@@ -29482,27 +29482,27 @@
       </c>
       <c r="BT69" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.54</t>
         </is>
       </c>
       <c r="BU69" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="BV69" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>15.81</t>
         </is>
       </c>
       <c r="BW69" t="inlineStr">
         <is>
-          <t>10.84%</t>
+          <t>8.69%</t>
         </is>
       </c>
       <c r="BX69" t="inlineStr">
         <is>
-          <t>7.27%</t>
+          <t>5.19%</t>
         </is>
       </c>
       <c r="BY69" t="inlineStr">
@@ -29512,52 +29512,52 @@
       </c>
       <c r="BZ69" t="inlineStr">
         <is>
-          <t>13374</t>
+          <t>12284</t>
         </is>
       </c>
       <c r="CA69" t="inlineStr">
         <is>
-          <t>工程50.74%、鋼板35.82%、特殊鋼帶板4.32%、矽鋼材4.32%、特殊鋼材2.90%、倉儲設備1.15%、型鋼0.57%、加工業務0.18% (2024年)</t>
+          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
         </is>
       </c>
       <c r="CB69" t="inlineStr">
         <is>
-          <t>春源-鋼鐵工業-上市</t>
+          <t>新光鋼-鋼鐵工業-上市</t>
         </is>
       </c>
       <c r="CC69" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上上市</t>
+          <t>鋼鐵工業右下上市</t>
         </is>
       </c>
       <c r="CD69" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CE69" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CF69" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>38.55</t>
         </is>
       </c>
       <c r="CG69" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CH69" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>36.35</t>
         </is>
       </c>
       <c r="CI69" t="inlineStr">
         <is>
-          <t>** 鋼鐵 - 冷熱軋鋼板捲、棒鋼盤元(捲狀條鋼)、冷熱軋不鏽鋼板捲、不鏽鋼棒線、裁剪加工、金屬製品、模具、建築工程** 建材營造 - 結構工程</t>
+          <t>** 鋼鐵 - 裁剪加工** 建材營造 - 基礎工程、結構工程** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 鋼材、塔架、其他配件</t>
         </is>
       </c>
       <c r="CJ69" t="inlineStr">
@@ -29569,22 +29569,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>1107.513</t>
+          <t>435.235</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -29594,7 +29594,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -29604,17 +29604,17 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-63.70</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -29624,37 +29624,37 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2025-09-25 00:00:00</t>
+          <t>2025-08-15 00:00:00</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>2025-10-13 00:00:00</t>
+          <t>2025-08-26 00:00:00</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>2025-07-30 00:00:00</t>
+          <t>2025-03-10 00:00:00</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>2025-08-27 00:00:00</t>
+          <t>2025-03-12 00:00:00</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -29664,12 +29664,12 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -29679,12 +29679,12 @@
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>-9.50</t>
         </is>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-15.62</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr">
@@ -29694,12 +29694,12 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>23.16</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
@@ -29710,121 +29710,121 @@
       <c r="AC70" t="inlineStr"/>
       <c r="AD70" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE70" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>326</t>
         </is>
       </c>
       <c r="AF70" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>97.73</t>
         </is>
       </c>
       <c r="AG70" t="inlineStr">
         <is>
-          <t>93.33</t>
+          <t>90.23</t>
         </is>
       </c>
       <c r="AH70" t="n">
-        <v>-0.05</v>
+        <v>0.49</v>
       </c>
       <c r="AI70" t="n">
-        <v>1.49</v>
+        <v>2.32</v>
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-3.40</t>
         </is>
       </c>
       <c r="AL70" t="inlineStr">
         <is>
-          <t>20.46</t>
+          <t>38.86</t>
         </is>
       </c>
       <c r="AM70" t="n">
-        <v>20.16</v>
+        <v>37.98</v>
       </c>
       <c r="AN70" t="n">
-        <v>19.98</v>
+        <v>39.63</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>20.28</t>
+          <t>41.03</t>
         </is>
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>51.97</t>
+          <t>63.94</t>
         </is>
       </c>
       <c r="AQ70" t="n">
-        <v>0.18</v>
+        <v>-0.17</v>
       </c>
       <c r="AR70" t="n">
-        <v>0.12</v>
+        <v>-0.47</v>
       </c>
       <c r="AS70" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr">
         <is>
-          <t>-85.40</t>
+          <t>-117.68</t>
         </is>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
-          <t>29422182.78288543</t>
+          <t>148998047.268034</t>
         </is>
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>22695242.0</t>
+          <t>16996914.0</t>
         </is>
       </c>
       <c r="AX70" t="n">
-        <v>16860764.4</v>
+        <v>16375301.2</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
-          <t>17515689.6</t>
+          <t>45115110.4</t>
         </is>
       </c>
       <c r="AZ70" t="n">
-        <v>20384448.64</v>
+        <v>32578634.98</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>-654925</t>
+          <t>-28739809</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
         <is>
-          <t>-564063.1285212772</t>
+          <t>405038.2427699324</t>
         </is>
       </c>
       <c r="BC70" t="inlineStr">
         <is>
-          <t>-442356.7308127098</t>
+          <t>-4921064.606875196</t>
         </is>
       </c>
       <c r="BD70" t="inlineStr">
         <is>
-          <t>22695242.0</t>
+          <t>16996914.0</t>
         </is>
       </c>
       <c r="BE70" t="inlineStr">
@@ -29834,27 +29834,27 @@
       </c>
       <c r="BF70" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="BG70" t="inlineStr">
         <is>
-          <t>2025/12/01</t>
+          <t>2025/08/07</t>
         </is>
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-5.90</t>
         </is>
       </c>
       <c r="BI70" t="inlineStr">
         <is>
-          <t>春源</t>
+          <t>新光鋼</t>
         </is>
       </c>
       <c r="BJ70" t="inlineStr">
         <is>
-          <t>春源</t>
+          <t>新光鋼</t>
         </is>
       </c>
       <c r="BK70" t="inlineStr">
@@ -29869,32 +29869,32 @@
       </c>
       <c r="BM70" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BN70" t="inlineStr">
         <is>
-          <t>1.166589855613648</t>
+          <t>-13.67996844119094</t>
         </is>
       </c>
       <c r="BO70" t="inlineStr">
         <is>
-          <t>-1.196134907171803</t>
+          <t>-10.11024290164889</t>
         </is>
       </c>
       <c r="BP70" t="inlineStr">
         <is>
-          <t>3.290941182656901</t>
+          <t>24.12947661306339</t>
         </is>
       </c>
       <c r="BQ70" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR70" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS70" t="inlineStr">
@@ -29904,27 +29904,27 @@
       </c>
       <c r="BT70" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.54</t>
         </is>
       </c>
       <c r="BU70" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="BV70" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>15.81</t>
         </is>
       </c>
       <c r="BW70" t="inlineStr">
         <is>
-          <t>10.84%</t>
+          <t>8.69%</t>
         </is>
       </c>
       <c r="BX70" t="inlineStr">
         <is>
-          <t>7.27%</t>
+          <t>5.19%</t>
         </is>
       </c>
       <c r="BY70" t="inlineStr">
@@ -29934,52 +29934,52 @@
       </c>
       <c r="BZ70" t="inlineStr">
         <is>
-          <t>13374</t>
+          <t>12284</t>
         </is>
       </c>
       <c r="CA70" t="inlineStr">
         <is>
-          <t>工程50.74%、鋼板35.82%、特殊鋼帶板4.32%、矽鋼材4.32%、特殊鋼材2.90%、倉儲設備1.15%、型鋼0.57%、加工業務0.18% (2024年)</t>
+          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
         </is>
       </c>
       <c r="CB70" t="inlineStr">
         <is>
-          <t>春源-鋼鐵工業-上市</t>
+          <t>新光鋼-鋼鐵工業-上市</t>
         </is>
       </c>
       <c r="CC70" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上上市</t>
+          <t>鋼鐵工業右下上市</t>
         </is>
       </c>
       <c r="CD70" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CE70" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CF70" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CG70" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CH70" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>36.35</t>
         </is>
       </c>
       <c r="CI70" t="inlineStr">
         <is>
-          <t>** 鋼鐵 - 冷熱軋鋼板捲、棒鋼盤元(捲狀條鋼)、冷熱軋不鏽鋼板捲、不鏽鋼棒線、裁剪加工、金屬製品、模具、建築工程** 建材營造 - 結構工程</t>
+          <t>** 鋼鐵 - 裁剪加工** 建材營造 - 基礎工程、結構工程** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 鋼材、塔架、其他配件</t>
         </is>
       </c>
       <c r="CJ70" t="inlineStr">
@@ -29991,22 +29991,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>553.964</t>
+          <t>358.496</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -30016,7 +30016,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -30026,17 +30026,17 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>-63.30</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -30046,37 +30046,37 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2025-09-25 00:00:00</t>
+          <t>2025-08-15 00:00:00</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>2025-10-13 00:00:00</t>
+          <t>2025-08-26 00:00:00</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>2025-07-30 00:00:00</t>
+          <t>2025-03-10 00:00:00</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>2025-08-27 00:00:00</t>
+          <t>2025-03-12 00:00:00</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -30086,12 +30086,12 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -30101,12 +30101,12 @@
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-10.31</t>
         </is>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-15.62</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11.59</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
@@ -30132,121 +30132,121 @@
       <c r="AC71" t="inlineStr"/>
       <c r="AD71" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE71" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>326</t>
         </is>
       </c>
       <c r="AF71" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.22</t>
         </is>
       </c>
       <c r="AG71" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>87.65</t>
         </is>
       </c>
       <c r="AH71" t="n">
-        <v>0.49</v>
+        <v>-0.44</v>
       </c>
       <c r="AI71" t="n">
-        <v>1.67</v>
+        <v>2.38</v>
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AL71" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>38.87</t>
         </is>
       </c>
       <c r="AM71" t="n">
-        <v>20.11</v>
+        <v>37.97</v>
       </c>
       <c r="AN71" t="n">
-        <v>19.97</v>
+        <v>39.7</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>20.28</t>
+          <t>41.08</t>
         </is>
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>71.17</t>
+          <t>55.74</t>
         </is>
       </c>
       <c r="AQ71" t="n">
-        <v>0.17</v>
+        <v>-0.24</v>
       </c>
       <c r="AR71" t="n">
-        <v>0.1</v>
+        <v>-0.55</v>
       </c>
       <c r="AS71" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr">
         <is>
-          <t>-87.30</t>
+          <t>-120.51</t>
         </is>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
-          <t>29422182.78288543</t>
+          <t>148998047.268034</t>
         </is>
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>11372791.0</t>
+          <t>13860324.0</t>
         </is>
       </c>
       <c r="AX71" t="n">
-        <v>15635916.8</v>
+        <v>16966580.2</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>16262746.4</t>
+          <t>46233081.4</t>
         </is>
       </c>
       <c r="AZ71" t="n">
-        <v>20133936.62</v>
+        <v>32635911.38</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>-626829</t>
+          <t>-29266501</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>-586191.5644682895</t>
+          <t>1373420.579069047</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
         <is>
-          <t>-1063849.748533946</t>
+          <t>-4428830.448891897</t>
         </is>
       </c>
       <c r="BD71" t="inlineStr">
         <is>
-          <t>11372791.0</t>
+          <t>13860324.0</t>
         </is>
       </c>
       <c r="BE71" t="inlineStr">
@@ -30256,27 +30256,27 @@
       </c>
       <c r="BF71" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="BG71" t="inlineStr">
         <is>
-          <t>2025/12/01</t>
+          <t>2025/08/07</t>
         </is>
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-6.75</t>
         </is>
       </c>
       <c r="BI71" t="inlineStr">
         <is>
-          <t>春源</t>
+          <t>新光鋼</t>
         </is>
       </c>
       <c r="BJ71" t="inlineStr">
         <is>
-          <t>春源</t>
+          <t>新光鋼</t>
         </is>
       </c>
       <c r="BK71" t="inlineStr">
@@ -30291,27 +30291,27 @@
       </c>
       <c r="BM71" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BN71" t="inlineStr">
         <is>
-          <t>1.166589855613648</t>
+          <t>-13.67996844119094</t>
         </is>
       </c>
       <c r="BO71" t="inlineStr">
         <is>
-          <t>-1.196134907171803</t>
+          <t>-10.11024290164889</t>
         </is>
       </c>
       <c r="BP71" t="inlineStr">
         <is>
-          <t>3.290941182656901</t>
+          <t>24.12947661306339</t>
         </is>
       </c>
       <c r="BQ71" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR71" t="inlineStr">
@@ -30321,32 +30321,32 @@
       </c>
       <c r="BS71" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BT71" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.54</t>
         </is>
       </c>
       <c r="BU71" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="BV71" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>15.81</t>
         </is>
       </c>
       <c r="BW71" t="inlineStr">
         <is>
-          <t>10.84%</t>
+          <t>8.69%</t>
         </is>
       </c>
       <c r="BX71" t="inlineStr">
         <is>
-          <t>7.27%</t>
+          <t>5.19%</t>
         </is>
       </c>
       <c r="BY71" t="inlineStr">
@@ -30356,52 +30356,52 @@
       </c>
       <c r="BZ71" t="inlineStr">
         <is>
-          <t>13374</t>
+          <t>12284</t>
         </is>
       </c>
       <c r="CA71" t="inlineStr">
         <is>
-          <t>工程50.74%、鋼板35.82%、特殊鋼帶板4.32%、矽鋼材4.32%、特殊鋼材2.90%、倉儲設備1.15%、型鋼0.57%、加工業務0.18% (2024年)</t>
+          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
         </is>
       </c>
       <c r="CB71" t="inlineStr">
         <is>
-          <t>春源-鋼鐵工業-上市</t>
+          <t>新光鋼-鋼鐵工業-上市</t>
         </is>
       </c>
       <c r="CC71" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上上市</t>
+          <t>鋼鐵工業右下上市</t>
         </is>
       </c>
       <c r="CD71" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CE71" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CF71" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="CG71" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CH71" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>36.35</t>
         </is>
       </c>
       <c r="CI71" t="inlineStr">
         <is>
-          <t>** 鋼鐵 - 冷熱軋鋼板捲、棒鋼盤元(捲狀條鋼)、冷熱軋不鏽鋼板捲、不鏽鋼棒線、裁剪加工、金屬製品、模具、建築工程** 建材營造 - 結構工程</t>
+          <t>** 鋼鐵 - 裁剪加工** 建材營造 - 基礎工程、結構工程** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 鋼材、塔架、其他配件</t>
         </is>
       </c>
       <c r="CJ71" t="inlineStr">
@@ -30413,22 +30413,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>688.801</t>
+          <t>363.213</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -30438,7 +30438,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -30448,17 +30448,17 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>11.19</t>
+          <t>-56.62</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -30468,37 +30468,37 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2025-09-25 00:00:00</t>
+          <t>2025-08-15 00:00:00</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>2025-10-13 00:00:00</t>
+          <t>2025-08-26 00:00:00</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>2025-07-30 00:00:00</t>
+          <t>2025-03-10 00:00:00</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>2025-08-27 00:00:00</t>
+          <t>2025-03-12 00:00:00</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -30508,12 +30508,12 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -30523,12 +30523,12 @@
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-9.97</t>
         </is>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-15.62</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr">
@@ -30538,137 +30538,137 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14.41</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr"/>
       <c r="AD72" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE72" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>326</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.74</t>
         </is>
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>97.92</t>
+          <t>91.36</t>
         </is>
       </c>
       <c r="AH72" t="n">
-        <v>0.54</v>
+        <v>-0.26</v>
       </c>
       <c r="AI72" t="n">
-        <v>1.72</v>
+        <v>2.58</v>
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AL72" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="AM72" t="n">
-        <v>20.05</v>
+        <v>37.97</v>
       </c>
       <c r="AN72" t="n">
-        <v>19.96</v>
+        <v>39.78</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>20.27</t>
+          <t>41.11</t>
         </is>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>87.46</t>
+          <t>52.64</t>
         </is>
       </c>
       <c r="AQ72" t="n">
-        <v>0.16</v>
+        <v>-0.3</v>
       </c>
       <c r="AR72" t="n">
-        <v>0.08</v>
+        <v>-0.63</v>
       </c>
       <c r="AS72" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr">
         <is>
-          <t>-89.56</t>
+          <t>-123.37</t>
         </is>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>29422182.78288543</t>
+          <t>148998047.268034</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>14110938.0</t>
+          <t>14075446.0</t>
         </is>
       </c>
       <c r="AX72" t="n">
-        <v>18605284.4</v>
+        <v>21356523.4</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>16732192.2</t>
+          <t>49229400.6</t>
         </is>
       </c>
       <c r="AZ72" t="n">
-        <v>20190650.78</v>
+        <v>32854915.68</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>1873092</t>
+          <t>-27872877</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>-499344.6219108974</t>
+          <t>2428375.311425582</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
         <is>
-          <t>-700582.5328309275</t>
+          <t>-3231403.064312473</t>
         </is>
       </c>
       <c r="BD72" t="inlineStr">
         <is>
-          <t>14110938.0</t>
+          <t>14075446.0</t>
         </is>
       </c>
       <c r="BE72" t="inlineStr">
@@ -30678,27 +30678,27 @@
       </c>
       <c r="BF72" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="BG72" t="inlineStr">
         <is>
-          <t>2025/12/01</t>
+          <t>2025/08/07</t>
         </is>
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="BI72" t="inlineStr">
         <is>
-          <t>春源</t>
+          <t>新光鋼</t>
         </is>
       </c>
       <c r="BJ72" t="inlineStr">
         <is>
-          <t>春源</t>
+          <t>新光鋼</t>
         </is>
       </c>
       <c r="BK72" t="inlineStr">
@@ -30713,27 +30713,27 @@
       </c>
       <c r="BM72" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BN72" t="inlineStr">
         <is>
-          <t>1.166589855613648</t>
+          <t>-13.67996844119094</t>
         </is>
       </c>
       <c r="BO72" t="inlineStr">
         <is>
-          <t>-1.196134907171803</t>
+          <t>-10.11024290164889</t>
         </is>
       </c>
       <c r="BP72" t="inlineStr">
         <is>
-          <t>3.290941182656901</t>
+          <t>24.12947661306339</t>
         </is>
       </c>
       <c r="BQ72" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR72" t="inlineStr">
@@ -30743,32 +30743,32 @@
       </c>
       <c r="BS72" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BT72" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.54</t>
         </is>
       </c>
       <c r="BU72" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="BV72" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>15.81</t>
         </is>
       </c>
       <c r="BW72" t="inlineStr">
         <is>
-          <t>10.84%</t>
+          <t>8.69%</t>
         </is>
       </c>
       <c r="BX72" t="inlineStr">
         <is>
-          <t>7.27%</t>
+          <t>5.19%</t>
         </is>
       </c>
       <c r="BY72" t="inlineStr">
@@ -30778,52 +30778,52 @@
       </c>
       <c r="BZ72" t="inlineStr">
         <is>
-          <t>13374</t>
+          <t>12284</t>
         </is>
       </c>
       <c r="CA72" t="inlineStr">
         <is>
-          <t>工程50.74%、鋼板35.82%、特殊鋼帶板4.32%、矽鋼材4.32%、特殊鋼材2.90%、倉儲設備1.15%、型鋼0.57%、加工業務0.18% (2024年)</t>
+          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
         </is>
       </c>
       <c r="CB72" t="inlineStr">
         <is>
-          <t>春源-鋼鐵工業-上市</t>
+          <t>新光鋼-鋼鐵工業-上市</t>
         </is>
       </c>
       <c r="CC72" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上上市</t>
+          <t>鋼鐵工業右下上市</t>
         </is>
       </c>
       <c r="CD72" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CE72" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="CF72" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CG72" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CH72" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>36.35</t>
         </is>
       </c>
       <c r="CI72" t="inlineStr">
         <is>
-          <t>** 鋼鐵 - 冷熱軋鋼板捲、棒鋼盤元(捲狀條鋼)、冷熱軋不鏽鋼板捲、不鏽鋼棒線、裁剪加工、金屬製品、模具、建築工程** 建材營造 - 結構工程</t>
+          <t>** 鋼鐵 - 裁剪加工** 建材營造 - 基礎工程、結構工程** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 鋼材、塔架、其他配件</t>
         </is>
       </c>
       <c r="CJ72" t="inlineStr">
@@ -30835,22 +30835,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>754.84</t>
+          <t>455.261</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -30860,7 +30860,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -30870,17 +30870,17 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>-47.41</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -30890,37 +30890,37 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2025-09-25 00:00:00</t>
+          <t>2025-08-15 00:00:00</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>2025-10-13 00:00:00</t>
+          <t>2025-08-26 00:00:00</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>2025-07-30 00:00:00</t>
+          <t>2025-03-10 00:00:00</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>2025-08-27 00:00:00</t>
+          <t>2025-03-12 00:00:00</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -30930,12 +30930,12 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -30945,12 +30945,12 @@
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-15.62</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr">
@@ -30960,137 +30960,137 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr"/>
       <c r="AD73" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE73" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>326</t>
         </is>
       </c>
       <c r="AF73" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AG73" t="inlineStr">
         <is>
-          <t>97.92</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AH73" t="n">
-        <v>0.6899999999999999</v>
+        <v>0</v>
       </c>
       <c r="AI73" t="n">
-        <v>1.68</v>
+        <v>2.16</v>
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AL73" t="inlineStr">
         <is>
-          <t>20.31</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="AM73" t="n">
-        <v>19.98</v>
+        <v>37.98</v>
       </c>
       <c r="AN73" t="n">
-        <v>19.96</v>
+        <v>39.86</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>20.27</t>
+          <t>41.16</t>
         </is>
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>110.41</t>
+          <t>47.01</t>
         </is>
       </c>
       <c r="AQ73" t="n">
-        <v>0.14</v>
+        <v>-0.38</v>
       </c>
       <c r="AR73" t="n">
-        <v>0.06</v>
+        <v>-0.71</v>
       </c>
       <c r="AS73" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr">
         <is>
-          <t>-91.84</t>
+          <t>-126.44</t>
         </is>
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
-          <t>29422182.78288543</t>
+          <t>148998047.268034</t>
         </is>
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>15423148.0</t>
+          <t>17787244.0</t>
         </is>
       </c>
       <c r="AX73" t="n">
-        <v>19289641.2</v>
+        <v>26453801.8</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>17652100.2</t>
+          <t>50298085.9</t>
         </is>
       </c>
       <c r="AZ73" t="n">
-        <v>20350387.22</v>
+        <v>33264214.78</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>1637541</t>
+          <t>-23844284</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>-462755.9108345283</t>
+          <t>3457425.925196137</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>-449981.4556540847</t>
+          <t>-1428434.048330702</t>
         </is>
       </c>
       <c r="BD73" t="inlineStr">
         <is>
-          <t>15423148.0</t>
+          <t>17787244.0</t>
         </is>
       </c>
       <c r="BE73" t="inlineStr">
@@ -31100,27 +31100,27 @@
       </c>
       <c r="BF73" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="BG73" t="inlineStr">
         <is>
-          <t>2025/12/01</t>
+          <t>2025/08/07</t>
         </is>
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-6.51</t>
         </is>
       </c>
       <c r="BI73" t="inlineStr">
         <is>
-          <t>春源</t>
+          <t>新光鋼</t>
         </is>
       </c>
       <c r="BJ73" t="inlineStr">
         <is>
-          <t>春源</t>
+          <t>新光鋼</t>
         </is>
       </c>
       <c r="BK73" t="inlineStr">
@@ -31135,32 +31135,32 @@
       </c>
       <c r="BM73" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BN73" t="inlineStr">
         <is>
-          <t>1.166589855613648</t>
+          <t>-13.67996844119094</t>
         </is>
       </c>
       <c r="BO73" t="inlineStr">
         <is>
-          <t>-1.196134907171803</t>
+          <t>-10.11024290164889</t>
         </is>
       </c>
       <c r="BP73" t="inlineStr">
         <is>
-          <t>3.290941182656901</t>
+          <t>24.12947661306339</t>
         </is>
       </c>
       <c r="BQ73" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR73" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS73" t="inlineStr">
@@ -31170,27 +31170,27 @@
       </c>
       <c r="BT73" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.54</t>
         </is>
       </c>
       <c r="BU73" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="BV73" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>15.81</t>
         </is>
       </c>
       <c r="BW73" t="inlineStr">
         <is>
-          <t>10.84%</t>
+          <t>8.69%</t>
         </is>
       </c>
       <c r="BX73" t="inlineStr">
         <is>
-          <t>7.27%</t>
+          <t>5.19%</t>
         </is>
       </c>
       <c r="BY73" t="inlineStr">
@@ -31200,52 +31200,52 @@
       </c>
       <c r="BZ73" t="inlineStr">
         <is>
-          <t>13374</t>
+          <t>12284</t>
         </is>
       </c>
       <c r="CA73" t="inlineStr">
         <is>
-          <t>工程50.74%、鋼板35.82%、特殊鋼帶板4.32%、矽鋼材4.32%、特殊鋼材2.90%、倉儲設備1.15%、型鋼0.57%、加工業務0.18% (2024年)</t>
+          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
         </is>
       </c>
       <c r="CB73" t="inlineStr">
         <is>
-          <t>春源-鋼鐵工業-上市</t>
+          <t>新光鋼-鋼鐵工業-上市</t>
         </is>
       </c>
       <c r="CC73" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上上市</t>
+          <t>鋼鐵工業右下上市</t>
         </is>
       </c>
       <c r="CD73" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CE73" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CF73" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CG73" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CH73" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>36.35</t>
         </is>
       </c>
       <c r="CI73" t="inlineStr">
         <is>
-          <t>** 鋼鐵 - 冷熱軋鋼板捲、棒鋼盤元(捲狀條鋼)、冷熱軋不鏽鋼板捲、不鏽鋼棒線、裁剪加工、金屬製品、模具、建築工程** 建材營造 - 結構工程</t>
+          <t>** 鋼鐵 - 裁剪加工** 建材營造 - 基礎工程、結構工程** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 鋼材、塔架、其他配件</t>
         </is>
       </c>
       <c r="CJ73" t="inlineStr">
@@ -31262,17 +31262,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>1019.978</t>
+          <t>492.79</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -31282,7 +31282,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -31292,17 +31292,17 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -31312,37 +31312,37 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2025-09-25 00:00:00</t>
+          <t>2025-08-15 00:00:00</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>2025-10-13 00:00:00</t>
+          <t>2025-08-26 00:00:00</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>2025-07-30 00:00:00</t>
+          <t>2025-03-10 00:00:00</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>2025-08-27 00:00:00</t>
+          <t>2025-03-12 00:00:00</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -31352,12 +31352,12 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -31367,12 +31367,12 @@
       </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-9.85</t>
         </is>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-15.62</t>
         </is>
       </c>
       <c r="Y74" t="inlineStr">
@@ -31382,12 +31382,12 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>21.33</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
@@ -31398,121 +31398,121 @@
       <c r="AC74" t="inlineStr"/>
       <c r="AD74" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE74" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>326</t>
         </is>
       </c>
       <c r="AF74" t="inlineStr">
         <is>
-          <t>93.75</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>97.92</t>
+          <t>97.78</t>
         </is>
       </c>
       <c r="AH74" t="n">
-        <v>0.59</v>
+        <v>1.25</v>
       </c>
       <c r="AI74" t="n">
-        <v>1.62</v>
+        <v>1.1</v>
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AL74" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>38.42</t>
         </is>
       </c>
       <c r="AM74" t="n">
-        <v>19.91</v>
+        <v>38</v>
       </c>
       <c r="AN74" t="n">
-        <v>19.95</v>
+        <v>39.92</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>20.26</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>145.22</t>
+          <t>41.20</t>
         </is>
       </c>
       <c r="AQ74" t="n">
-        <v>0.11</v>
+        <v>-0.47</v>
       </c>
       <c r="AR74" t="n">
-        <v>0.05</v>
+        <v>-0.79</v>
       </c>
       <c r="AS74" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr">
         <is>
-          <t>-94.09</t>
+          <t>-129.55</t>
         </is>
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>29422182.78288543</t>
+          <t>148998047.268034</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>20701703.0</t>
+          <t>19156578.0</t>
         </is>
       </c>
       <c r="AX74" t="n">
-        <v>18553023</v>
+        <v>69426442.8</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>18327514.0</t>
+          <t>52456837.4</t>
         </is>
       </c>
       <c r="AZ74" t="n">
-        <v>20240377.18</v>
+        <v>33433682.52</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>225509</t>
+          <t>16969605</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>-465078.5390491545</t>
+          <t>4345764.102201018</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
         <is>
-          <t>-216503.0791280903</t>
+          <t>800558.8333693519</t>
         </is>
       </c>
       <c r="BD74" t="inlineStr">
         <is>
-          <t>20701703.0</t>
+          <t>19156578.0</t>
         </is>
       </c>
       <c r="BE74" t="inlineStr">
@@ -31522,27 +31522,27 @@
       </c>
       <c r="BF74" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="BG74" t="inlineStr">
         <is>
-          <t>2025/12/01</t>
+          <t>2025/08/07</t>
         </is>
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="BI74" t="inlineStr">
         <is>
-          <t>春源</t>
+          <t>新光鋼</t>
         </is>
       </c>
       <c r="BJ74" t="inlineStr">
         <is>
-          <t>春源</t>
+          <t>新光鋼</t>
         </is>
       </c>
       <c r="BK74" t="inlineStr">
@@ -31557,22 +31557,22 @@
       </c>
       <c r="BM74" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BN74" t="inlineStr">
         <is>
-          <t>1.166589855613648</t>
+          <t>-13.67996844119094</t>
         </is>
       </c>
       <c r="BO74" t="inlineStr">
         <is>
-          <t>-1.196134907171803</t>
+          <t>-10.11024290164889</t>
         </is>
       </c>
       <c r="BP74" t="inlineStr">
         <is>
-          <t>3.290941182656901</t>
+          <t>24.12947661306339</t>
         </is>
       </c>
       <c r="BQ74" t="inlineStr">
@@ -31582,7 +31582,7 @@
       </c>
       <c r="BR74" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS74" t="inlineStr">
@@ -31592,27 +31592,27 @@
       </c>
       <c r="BT74" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.54</t>
         </is>
       </c>
       <c r="BU74" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="BV74" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>15.81</t>
         </is>
       </c>
       <c r="BW74" t="inlineStr">
         <is>
-          <t>10.84%</t>
+          <t>8.69%</t>
         </is>
       </c>
       <c r="BX74" t="inlineStr">
         <is>
-          <t>7.27%</t>
+          <t>5.19%</t>
         </is>
       </c>
       <c r="BY74" t="inlineStr">
@@ -31622,52 +31622,52 @@
       </c>
       <c r="BZ74" t="inlineStr">
         <is>
-          <t>13374</t>
+          <t>12284</t>
         </is>
       </c>
       <c r="CA74" t="inlineStr">
         <is>
-          <t>工程50.74%、鋼板35.82%、特殊鋼帶板4.32%、矽鋼材4.32%、特殊鋼材2.90%、倉儲設備1.15%、型鋼0.57%、加工業務0.18% (2024年)</t>
+          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
         </is>
       </c>
       <c r="CB74" t="inlineStr">
         <is>
-          <t>春源-鋼鐵工業-上市</t>
+          <t>新光鋼-鋼鐵工業-上市</t>
         </is>
       </c>
       <c r="CC74" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上上市</t>
+          <t>鋼鐵工業右下上市</t>
         </is>
       </c>
       <c r="CD74" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CE74" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CF74" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CG74" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CH74" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>36.35</t>
         </is>
       </c>
       <c r="CI74" t="inlineStr">
         <is>
-          <t>** 鋼鐵 - 冷熱軋鋼板捲、棒鋼盤元(捲狀條鋼)、冷熱軋不鏽鋼板捲、不鏽鋼棒線、裁剪加工、金屬製品、模具、建築工程** 建材營造 - 結構工程</t>
+          <t>** 鋼鐵 - 裁剪加工** 建材營造 - 基礎工程、結構工程** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 鋼材、塔架、其他配件</t>
         </is>
       </c>
       <c r="CJ74" t="inlineStr">
@@ -31679,22 +31679,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>812.811</t>
+          <t>510.601</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -31704,7 +31704,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -31714,17 +31714,17 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>32.21</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -31734,37 +31734,37 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2025-09-25 00:00:00</t>
+          <t>2025-08-15 00:00:00</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>2025-10-13 00:00:00</t>
+          <t>2025-08-26 00:00:00</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>2025-07-30 00:00:00</t>
+          <t>2025-03-10 00:00:00</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>2025-08-27 00:00:00</t>
+          <t>2025-03-12 00:00:00</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -31774,12 +31774,12 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
@@ -31789,12 +31789,12 @@
       </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-9.39</t>
         </is>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-15.62</t>
         </is>
       </c>
       <c r="Y75" t="inlineStr">
@@ -31804,12 +31804,12 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
@@ -31820,12 +31820,12 @@
       <c r="AC75" t="inlineStr"/>
       <c r="AD75" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE75" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>326</t>
         </is>
       </c>
       <c r="AF75" t="inlineStr">
@@ -31835,106 +31835,106 @@
       </c>
       <c r="AG75" t="inlineStr">
         <is>
-          <t>96.97</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH75" t="n">
-        <v>1.39</v>
+        <v>2.87</v>
       </c>
       <c r="AI75" t="n">
-        <v>1.37</v>
+        <v>-0.09</v>
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AL75" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>38.01000000000001</t>
         </is>
       </c>
       <c r="AM75" t="n">
-        <v>19.85</v>
+        <v>38.04</v>
       </c>
       <c r="AN75" t="n">
-        <v>19.95</v>
+        <v>39.97</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>222.51</t>
+          <t>33.12</t>
         </is>
       </c>
       <c r="AQ75" t="n">
-        <v>0.1</v>
+        <v>-0.59</v>
       </c>
       <c r="AR75" t="n">
-        <v>0.03</v>
+        <v>-0.88</v>
       </c>
       <c r="AS75" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr">
         <is>
-          <t>-96.24</t>
+          <t>-132.60</t>
         </is>
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
-          <t>29422182.78288543</t>
+          <t>148998047.268034</t>
         </is>
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>16571004.0</t>
+          <t>19953309.0</t>
         </is>
       </c>
       <c r="AX75" t="n">
-        <v>18170614.8</v>
+        <v>73854919.59999999</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t>17758365.3</t>
+          <t>55863021.8</t>
         </is>
       </c>
       <c r="AZ75" t="n">
-        <v>20187873.48</v>
+        <v>33328621.84</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>412249</t>
+          <t>17991897</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
         <is>
-          <t>-510274.0772166207</t>
+          <t>4990346.878352229</t>
         </is>
       </c>
       <c r="BC75" t="inlineStr">
         <is>
-          <t>-440789.7526935264</t>
+          <t>3809528.634606227</t>
         </is>
       </c>
       <c r="BD75" t="inlineStr">
         <is>
-          <t>16571004.0</t>
+          <t>19953309.0</t>
         </is>
       </c>
       <c r="BE75" t="inlineStr">
@@ -31944,27 +31944,27 @@
       </c>
       <c r="BF75" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="BG75" t="inlineStr">
         <is>
-          <t>2025/12/01</t>
+          <t>2025/08/07</t>
         </is>
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-5.78</t>
         </is>
       </c>
       <c r="BI75" t="inlineStr">
         <is>
-          <t>春源</t>
+          <t>新光鋼</t>
         </is>
       </c>
       <c r="BJ75" t="inlineStr">
         <is>
-          <t>春源</t>
+          <t>新光鋼</t>
         </is>
       </c>
       <c r="BK75" t="inlineStr">
@@ -31979,62 +31979,62 @@
       </c>
       <c r="BM75" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BN75" t="inlineStr">
         <is>
-          <t>1.166589855613648</t>
+          <t>-13.67996844119094</t>
         </is>
       </c>
       <c r="BO75" t="inlineStr">
         <is>
-          <t>-1.196134907171803</t>
+          <t>-10.11024290164889</t>
         </is>
       </c>
       <c r="BP75" t="inlineStr">
         <is>
-          <t>3.290941182656901</t>
+          <t>24.12947661306339</t>
         </is>
       </c>
       <c r="BQ75" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR75" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS75" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BT75" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.54</t>
         </is>
       </c>
       <c r="BU75" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="BV75" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>15.81</t>
         </is>
       </c>
       <c r="BW75" t="inlineStr">
         <is>
-          <t>10.84%</t>
+          <t>8.69%</t>
         </is>
       </c>
       <c r="BX75" t="inlineStr">
         <is>
-          <t>7.27%</t>
+          <t>5.19%</t>
         </is>
       </c>
       <c r="BY75" t="inlineStr">
@@ -32044,52 +32044,52 @@
       </c>
       <c r="BZ75" t="inlineStr">
         <is>
-          <t>13374</t>
+          <t>12284</t>
         </is>
       </c>
       <c r="CA75" t="inlineStr">
         <is>
-          <t>工程50.74%、鋼板35.82%、特殊鋼帶板4.32%、矽鋼材4.32%、特殊鋼材2.90%、倉儲設備1.15%、型鋼0.57%、加工業務0.18% (2024年)</t>
+          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
         </is>
       </c>
       <c r="CB75" t="inlineStr">
         <is>
-          <t>春源-鋼鐵工業-上市</t>
+          <t>新光鋼-鋼鐵工業-上市</t>
         </is>
       </c>
       <c r="CC75" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上上市</t>
+          <t>鋼鐵工業右下上市</t>
         </is>
       </c>
       <c r="CD75" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CE75" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CF75" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="CG75" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CH75" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>36.35</t>
         </is>
       </c>
       <c r="CI75" t="inlineStr">
         <is>
-          <t>** 鋼鐵 - 冷熱軋鋼板捲、棒鋼盤元(捲狀條鋼)、冷熱軋不鏽鋼板捲、不鏽鋼棒線、裁剪加工、金屬製品、模具、建築工程** 建材營造 - 結構工程</t>
+          <t>** 鋼鐵 - 裁剪加工** 建材營造 - 基礎工程、結構工程** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 鋼材、塔架、其他配件</t>
         </is>
       </c>
       <c r="CJ75" t="inlineStr">
@@ -32101,22 +32101,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>1293.122</t>
+          <t>914.803</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -32126,7 +32126,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -32136,17 +32136,17 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>35.32</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -32156,37 +32156,37 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2025-09-25 00:00:00</t>
+          <t>2025-08-15 00:00:00</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>2025-10-13 00:00:00</t>
+          <t>2025-08-26 00:00:00</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>2025-07-30 00:00:00</t>
+          <t>2025-03-10 00:00:00</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>2025-08-27 00:00:00</t>
+          <t>2025-03-12 00:00:00</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -32196,12 +32196,12 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
@@ -32211,12 +32211,12 @@
       </c>
       <c r="W76" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-9.39</t>
         </is>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-15.62</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr">
@@ -32226,12 +32226,12 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>27.05</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
@@ -32242,12 +32242,12 @@
       <c r="AC76" t="inlineStr"/>
       <c r="AD76" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE76" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>326</t>
         </is>
       </c>
       <c r="AF76" t="inlineStr">
@@ -32257,106 +32257,106 @@
       </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>88.64</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AH76" t="n">
-        <v>1.15</v>
+        <v>4.35</v>
       </c>
       <c r="AI76" t="n">
-        <v>1.19</v>
+        <v>-1.59</v>
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AL76" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>37.47</t>
         </is>
       </c>
       <c r="AM76" t="n">
-        <v>19.78</v>
+        <v>38.08</v>
       </c>
       <c r="AN76" t="n">
-        <v>19.94</v>
+        <v>40.03</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>20.24</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>398.09</t>
+          <t>20.99</t>
         </is>
       </c>
       <c r="AQ76" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.75</v>
       </c>
       <c r="AR76" t="n">
-        <v>0.01</v>
+        <v>-0.95</v>
       </c>
       <c r="AS76" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr">
         <is>
-          <t>-98.33</t>
+          <t>-135.29</t>
         </is>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
-          <t>29422182.78288543</t>
+          <t>148998047.268034</t>
         </is>
       </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>26219629.0</t>
+          <t>35810040.0</t>
         </is>
       </c>
       <c r="AX76" t="n">
-        <v>16889576</v>
+        <v>75499582.59999999</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>17236189.3</t>
+          <t>55792550.2</t>
         </is>
       </c>
       <c r="AZ76" t="n">
-        <v>20277790.28</v>
+        <v>33454972.78</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>-346613</t>
+          <t>19707032</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
         <is>
-          <t>-522907.5907662741</t>
+          <t>5205041.104487866</t>
         </is>
       </c>
       <c r="BC76" t="inlineStr">
         <is>
-          <t>-302881.9023336619</t>
+          <t>7886638.29228013</t>
         </is>
       </c>
       <c r="BD76" t="inlineStr">
         <is>
-          <t>26219629.0</t>
+          <t>35810040.0</t>
         </is>
       </c>
       <c r="BE76" t="inlineStr">
@@ -32366,27 +32366,27 @@
       </c>
       <c r="BF76" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="BG76" t="inlineStr">
         <is>
-          <t>2025/12/01</t>
+          <t>2025/08/07</t>
         </is>
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-5.78</t>
         </is>
       </c>
       <c r="BI76" t="inlineStr">
         <is>
-          <t>春源</t>
+          <t>新光鋼</t>
         </is>
       </c>
       <c r="BJ76" t="inlineStr">
         <is>
-          <t>春源</t>
+          <t>新光鋼</t>
         </is>
       </c>
       <c r="BK76" t="inlineStr">
@@ -32401,62 +32401,62 @@
       </c>
       <c r="BM76" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BN76" t="inlineStr">
         <is>
-          <t>1.166589855613648</t>
+          <t>-13.67996844119094</t>
         </is>
       </c>
       <c r="BO76" t="inlineStr">
         <is>
-          <t>-1.196134907171803</t>
+          <t>-10.11024290164889</t>
         </is>
       </c>
       <c r="BP76" t="inlineStr">
         <is>
-          <t>3.290941182656901</t>
+          <t>24.12947661306339</t>
         </is>
       </c>
       <c r="BQ76" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR76" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS76" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BT76" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.54</t>
         </is>
       </c>
       <c r="BU76" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="BV76" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>15.81</t>
         </is>
       </c>
       <c r="BW76" t="inlineStr">
         <is>
-          <t>10.84%</t>
+          <t>8.69%</t>
         </is>
       </c>
       <c r="BX76" t="inlineStr">
         <is>
-          <t>7.27%</t>
+          <t>5.19%</t>
         </is>
       </c>
       <c r="BY76" t="inlineStr">
@@ -32466,52 +32466,52 @@
       </c>
       <c r="BZ76" t="inlineStr">
         <is>
-          <t>13374</t>
+          <t>12284</t>
         </is>
       </c>
       <c r="CA76" t="inlineStr">
         <is>
-          <t>工程50.74%、鋼板35.82%、特殊鋼帶板4.32%、矽鋼材4.32%、特殊鋼材2.90%、倉儲設備1.15%、型鋼0.57%、加工業務0.18% (2024年)</t>
+          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
         </is>
       </c>
       <c r="CB76" t="inlineStr">
         <is>
-          <t>春源-鋼鐵工業-上市</t>
+          <t>新光鋼-鋼鐵工業-上市</t>
         </is>
       </c>
       <c r="CC76" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上上市</t>
+          <t>鋼鐵工業右下上市</t>
         </is>
       </c>
       <c r="CD76" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CE76" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CF76" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>38.15</t>
         </is>
       </c>
       <c r="CG76" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CH76" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>36.35</t>
         </is>
       </c>
       <c r="CI76" t="inlineStr">
         <is>
-          <t>** 鋼鐵 - 冷熱軋鋼板捲、棒鋼盤元(捲狀條鋼)、冷熱軋不鏽鋼板捲、不鏽鋼棒線、裁剪加工、金屬製品、模具、建築工程** 建材營造 - 結構工程</t>
+          <t>** 鋼鐵 - 裁剪加工** 建材營造 - 基礎工程、結構工程** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 鋼材、塔架、其他配件</t>
         </is>
       </c>
       <c r="CJ76" t="inlineStr">
@@ -32523,22 +32523,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>876.712</t>
+          <t>1043.085</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -32548,7 +32548,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -32558,17 +32558,17 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>-10.71</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -32578,37 +32578,37 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2025-09-25 00:00:00</t>
+          <t>2025-08-15 00:00:00</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>2025-10-13 00:00:00</t>
+          <t>2025-08-26 00:00:00</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>2025-07-30 00:00:00</t>
+          <t>2025-03-10 00:00:00</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>2025-08-27 00:00:00</t>
+          <t>2025-03-12 00:00:00</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -32618,12 +32618,12 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
@@ -32633,12 +32633,12 @@
       </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-11.70</t>
         </is>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-15.62</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
@@ -32648,12 +32648,12 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>18.34</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
@@ -32664,121 +32664,121 @@
       <c r="AC77" t="inlineStr"/>
       <c r="AD77" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE77" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>326</t>
         </is>
       </c>
       <c r="AF77" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>66.41</t>
+          <t>59.17</t>
         </is>
       </c>
       <c r="AH77" t="n">
-        <v>1.06</v>
+        <v>3.34</v>
       </c>
       <c r="AI77" t="n">
-        <v>0.8</v>
+        <v>-3.27</v>
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-4.89</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AL77" t="inlineStr">
         <is>
-          <t>19.89</t>
+          <t>36.87</t>
         </is>
       </c>
       <c r="AM77" t="n">
-        <v>19.73</v>
+        <v>38.11</v>
       </c>
       <c r="AN77" t="n">
-        <v>19.94</v>
+        <v>40.07</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>20.24</t>
+          <t>41.23</t>
         </is>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>65587.40</t>
+          <t>5.10</t>
         </is>
       </c>
       <c r="AQ77" t="n">
-        <v>0.04</v>
+        <v>-0.95</v>
       </c>
       <c r="AR77" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AS77" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr">
         <is>
-          <t>-99.99</t>
+          <t>-137.15</t>
         </is>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>29422182.78288543</t>
+          <t>148998047.268034</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>17532722.0</t>
+          <t>39561838.0</t>
         </is>
       </c>
       <c r="AX77" t="n">
-        <v>14859100</v>
+        <v>77102277.8</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>16642108.4</t>
+          <t>54515793.2</t>
         </is>
       </c>
       <c r="AZ77" t="n">
-        <v>20371841.18</v>
+        <v>33864219.92</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>-1783008</t>
+          <t>22586484</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>-562912.2613903855</t>
+          <t>4717477.979434728</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
         <is>
-          <t>-1128834.726736229</t>
+          <t>11730479.54280426</t>
         </is>
       </c>
       <c r="BD77" t="inlineStr">
         <is>
-          <t>17532722.0</t>
+          <t>39561838.0</t>
         </is>
       </c>
       <c r="BE77" t="inlineStr">
@@ -32788,27 +32788,27 @@
       </c>
       <c r="BF77" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="BG77" t="inlineStr">
         <is>
-          <t>2025/12/01</t>
+          <t>2025/08/07</t>
         </is>
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-8.19</t>
         </is>
       </c>
       <c r="BI77" t="inlineStr">
         <is>
-          <t>春源</t>
+          <t>新光鋼</t>
         </is>
       </c>
       <c r="BJ77" t="inlineStr">
         <is>
-          <t>春源</t>
+          <t>新光鋼</t>
         </is>
       </c>
       <c r="BK77" t="inlineStr">
@@ -32823,27 +32823,27 @@
       </c>
       <c r="BM77" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BN77" t="inlineStr">
         <is>
-          <t>1.166589855613648</t>
+          <t>-13.67996844119094</t>
         </is>
       </c>
       <c r="BO77" t="inlineStr">
         <is>
-          <t>-1.196134907171803</t>
+          <t>-10.11024290164889</t>
         </is>
       </c>
       <c r="BP77" t="inlineStr">
         <is>
-          <t>3.290941182656901</t>
+          <t>24.12947661306339</t>
         </is>
       </c>
       <c r="BQ77" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR77" t="inlineStr">
@@ -32853,32 +32853,32 @@
       </c>
       <c r="BS77" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT77" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.54</t>
         </is>
       </c>
       <c r="BU77" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="BV77" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>15.81</t>
         </is>
       </c>
       <c r="BW77" t="inlineStr">
         <is>
-          <t>10.84%</t>
+          <t>8.69%</t>
         </is>
       </c>
       <c r="BX77" t="inlineStr">
         <is>
-          <t>7.27%</t>
+          <t>5.19%</t>
         </is>
       </c>
       <c r="BY77" t="inlineStr">
@@ -32888,52 +32888,52 @@
       </c>
       <c r="BZ77" t="inlineStr">
         <is>
-          <t>13374</t>
+          <t>12284</t>
         </is>
       </c>
       <c r="CA77" t="inlineStr">
         <is>
-          <t>工程50.74%、鋼板35.82%、特殊鋼帶板4.32%、矽鋼材4.32%、特殊鋼材2.90%、倉儲設備1.15%、型鋼0.57%、加工業務0.18% (2024年)</t>
+          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
         </is>
       </c>
       <c r="CB77" t="inlineStr">
         <is>
-          <t>春源-鋼鐵工業-上市</t>
+          <t>新光鋼-鋼鐵工業-上市</t>
         </is>
       </c>
       <c r="CC77" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上上市</t>
+          <t>鋼鐵工業右下上市</t>
         </is>
       </c>
       <c r="CD77" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="CE77" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CF77" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="CG77" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CH77" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>36.35</t>
         </is>
       </c>
       <c r="CI77" t="inlineStr">
         <is>
-          <t>** 鋼鐵 - 冷熱軋鋼板捲、棒鋼盤元(捲狀條鋼)、冷熱軋不鏽鋼板捲、不鏽鋼棒線、裁剪加工、金屬製品、模具、建築工程** 建材營造 - 結構工程</t>
+          <t>** 鋼鐵 - 裁剪加工** 建材營造 - 基礎工程、結構工程** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 鋼材、塔架、其他配件</t>
         </is>
       </c>
       <c r="CJ77" t="inlineStr">
@@ -32945,22 +32945,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>587.867</t>
+          <t>6301.223</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -32970,7 +32970,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -32980,17 +32980,17 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>29.52</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -33000,37 +33000,37 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2025-09-25 00:00:00</t>
+          <t>2025-08-15 00:00:00</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>2025-10-13 00:00:00</t>
+          <t>2025-08-26 00:00:00</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>2025-07-30 00:00:00</t>
+          <t>2025-03-10 00:00:00</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>2025-08-27 00:00:00</t>
+          <t>2025-03-12 00:00:00</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -33040,12 +33040,12 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
@@ -33055,12 +33055,12 @@
       </c>
       <c r="W78" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-15.62</t>
         </is>
       </c>
       <c r="Y78" t="inlineStr">
@@ -33070,12 +33070,12 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12.30</t>
+          <t>67.14</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
@@ -33086,279 +33086,4921 @@
       <c r="AC78" t="inlineStr"/>
       <c r="AD78" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE78" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="AF78" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="AG78" t="inlineStr">
+        <is>
+          <t>29.75</t>
+        </is>
+      </c>
+      <c r="AH78" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AI78" t="n">
+        <v>-4.24</v>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>-4.85</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>-2.68</t>
+        </is>
+      </c>
+      <c r="AL78" t="inlineStr">
+        <is>
+          <t>36.60000000000001</t>
+        </is>
+      </c>
+      <c r="AM78" t="n">
+        <v>38.22</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>40.17</v>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>41.28</t>
+        </is>
+      </c>
+      <c r="AP78" t="inlineStr">
+        <is>
+          <t>-7.24</t>
+        </is>
+      </c>
+      <c r="AQ78" t="n">
+        <v>-1.08</v>
+      </c>
+      <c r="AR78" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="AS78" t="inlineStr">
+        <is>
+          <t>2.69</t>
+        </is>
+      </c>
+      <c r="AT78" t="inlineStr">
+        <is>
+          <t>-137.62</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV78" t="inlineStr">
+        <is>
+          <t>148998047.268034</t>
+        </is>
+      </c>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>232650449.0</t>
+        </is>
+      </c>
+      <c r="AX78" t="n">
+        <v>74142370</v>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>57245793.0</t>
+        </is>
+      </c>
+      <c r="AZ78" t="n">
+        <v>34130931.06</v>
+      </c>
+      <c r="BA78" t="inlineStr">
+        <is>
+          <t>16896577</t>
+        </is>
+      </c>
+      <c r="BB78" t="inlineStr">
+        <is>
+          <t>3442386.786094812</t>
+        </is>
+      </c>
+      <c r="BC78" t="inlineStr">
+        <is>
+          <t>16400757.27416717</t>
+        </is>
+      </c>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>232650449.0</t>
+        </is>
+      </c>
+      <c r="BE78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF78" t="inlineStr">
+        <is>
+          <t>41.5</t>
+        </is>
+      </c>
+      <c r="BG78" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH78" t="inlineStr">
+        <is>
+          <t>-11.08</t>
+        </is>
+      </c>
+      <c r="BI78" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BJ78" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BK78" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL78" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM78" t="inlineStr">
+        <is>
+          <t>0.62</t>
+        </is>
+      </c>
+      <c r="BN78" t="inlineStr">
+        <is>
+          <t>-13.67996844119094</t>
+        </is>
+      </c>
+      <c r="BO78" t="inlineStr">
+        <is>
+          <t>-10.11024290164889</t>
+        </is>
+      </c>
+      <c r="BP78" t="inlineStr">
+        <is>
+          <t>24.12947661306339</t>
+        </is>
+      </c>
+      <c r="BQ78" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR78" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS78" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="BT78" t="inlineStr">
+        <is>
+          <t>6.54</t>
+        </is>
+      </c>
+      <c r="BU78" t="inlineStr">
+        <is>
+          <t>11.90</t>
+        </is>
+      </c>
+      <c r="BV78" t="inlineStr">
+        <is>
+          <t>15.81</t>
+        </is>
+      </c>
+      <c r="BW78" t="inlineStr">
+        <is>
+          <t>8.69%</t>
+        </is>
+      </c>
+      <c r="BX78" t="inlineStr">
+        <is>
+          <t>5.19%</t>
+        </is>
+      </c>
+      <c r="BY78" t="inlineStr">
+        <is>
+          <t>30.47</t>
+        </is>
+      </c>
+      <c r="BZ78" t="inlineStr">
+        <is>
+          <t>12284</t>
+        </is>
+      </c>
+      <c r="CA78" t="inlineStr">
+        <is>
+          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB78" t="inlineStr">
+        <is>
+          <t>新光鋼-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC78" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CD78" t="inlineStr">
+        <is>
+          <t>37.0</t>
+        </is>
+      </c>
+      <c r="CE78" t="inlineStr">
+        <is>
+          <t>37.5</t>
+        </is>
+      </c>
+      <c r="CF78" t="inlineStr">
+        <is>
+          <t>36.9</t>
+        </is>
+      </c>
+      <c r="CG78" t="inlineStr">
+        <is>
+          <t>36.9</t>
+        </is>
+      </c>
+      <c r="CH78" t="inlineStr">
+        <is>
+          <t>36.35</t>
+        </is>
+      </c>
+      <c r="CI78" t="inlineStr">
+        <is>
+          <t>** 鋼鐵 - 裁剪加工** 建材營造 - 基礎工程、結構工程** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 鋼材、塔架、其他配件</t>
+        </is>
+      </c>
+      <c r="CJ78" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>價_量;【b1】</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>1237.222</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>20.65</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>-5.77</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>2025-07-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>2025-08-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>20.65</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>19.8</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>-2.36</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>25.88</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>0.73</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr"/>
+      <c r="AD79" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="AE78" t="inlineStr">
+      <c r="AE79" t="inlineStr">
         <is>
           <t>1237</t>
         </is>
       </c>
-      <c r="AF78" t="inlineStr">
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t>85.93</t>
+        </is>
+      </c>
+      <c r="AH79" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AI79" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>-1.40</t>
+        </is>
+      </c>
+      <c r="AL79" t="inlineStr">
+        <is>
+          <t>20.52</t>
+        </is>
+      </c>
+      <c r="AM79" t="n">
+        <v>20.19</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>20.27</t>
+        </is>
+      </c>
+      <c r="AP79" t="inlineStr">
+        <is>
+          <t>35.99</t>
+        </is>
+      </c>
+      <c r="AQ79" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AR79" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AS79" t="inlineStr">
+        <is>
+          <t>0.79</t>
+        </is>
+      </c>
+      <c r="AT79" t="inlineStr">
+        <is>
+          <t>-82.27</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV79" t="inlineStr">
+        <is>
+          <t>29422182.78288543</t>
+        </is>
+      </c>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>25460455.0</t>
+        </is>
+      </c>
+      <c r="AX79" t="n">
+        <v>17184128.2</v>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>18236884.7</t>
+        </is>
+      </c>
+      <c r="AZ79" t="n">
+        <v>20624284.56</v>
+      </c>
+      <c r="BA79" t="inlineStr">
+        <is>
+          <t>-1052756</t>
+        </is>
+      </c>
+      <c r="BB79" t="inlineStr">
+        <is>
+          <t>-505642.3241600473</t>
+        </is>
+      </c>
+      <c r="BC79" t="inlineStr">
+        <is>
+          <t>-3892.7030364573</t>
+        </is>
+      </c>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>25460455.0</t>
+        </is>
+      </c>
+      <c r="BE79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF79" t="inlineStr">
+        <is>
+          <t>20.45</t>
+        </is>
+      </c>
+      <c r="BG79" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="BH79" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="BI79" t="inlineStr">
+        <is>
+          <t>春源</t>
+        </is>
+      </c>
+      <c r="BJ79" t="inlineStr">
+        <is>
+          <t>春源</t>
+        </is>
+      </c>
+      <c r="BK79" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL79" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM79" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="BN79" t="inlineStr">
+        <is>
+          <t>1.166589855613648</t>
+        </is>
+      </c>
+      <c r="BO79" t="inlineStr">
+        <is>
+          <t>-1.196134907171803</t>
+        </is>
+      </c>
+      <c r="BP79" t="inlineStr">
+        <is>
+          <t>3.290941182656901</t>
+        </is>
+      </c>
+      <c r="BQ79" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR79" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS79" t="inlineStr">
+        <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="BT79" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="BU79" t="inlineStr">
+        <is>
+          <t>9.57</t>
+        </is>
+      </c>
+      <c r="BV79" t="inlineStr">
+        <is>
+          <t>9.3</t>
+        </is>
+      </c>
+      <c r="BW79" t="inlineStr">
+        <is>
+          <t>10.84%</t>
+        </is>
+      </c>
+      <c r="BX79" t="inlineStr">
+        <is>
+          <t>7.27%</t>
+        </is>
+      </c>
+      <c r="BY79" t="inlineStr">
+        <is>
+          <t>30.47</t>
+        </is>
+      </c>
+      <c r="BZ79" t="inlineStr">
+        <is>
+          <t>13374</t>
+        </is>
+      </c>
+      <c r="CA79" t="inlineStr">
+        <is>
+          <t>工程50.74%、鋼板35.82%、特殊鋼帶板4.32%、矽鋼材4.32%、特殊鋼材2.90%、倉儲設備1.15%、型鋼0.57%、加工業務0.18% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB79" t="inlineStr">
+        <is>
+          <t>春源-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC79" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右上上市</t>
+        </is>
+      </c>
+      <c r="CD79" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="CE79" t="inlineStr">
+        <is>
+          <t>20.65</t>
+        </is>
+      </c>
+      <c r="CF79" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="CG79" t="inlineStr">
+        <is>
+          <t>20.65</t>
+        </is>
+      </c>
+      <c r="CH79" t="inlineStr">
+        <is>
+          <t>19.04</t>
+        </is>
+      </c>
+      <c r="CI79" t="inlineStr">
+        <is>
+          <t>** 鋼鐵 - 冷熱軋鋼板捲、棒鋼盤元(捲狀條鋼)、冷熱軋不鏽鋼板捲、不鏽鋼棒線、裁剪加工、金屬製品、模具、建築工程** 建材營造 - 結構工程</t>
+        </is>
+      </c>
+      <c r="CJ79" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>【b1】</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>603.128</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>20.45</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>-10.01</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>2025-07-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>2025-08-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>20.65</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>19.8</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>0.74</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>-2.36</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>12.62</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>0.74</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr"/>
+      <c r="AD80" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AE80" t="inlineStr">
+        <is>
+          <t>1237</t>
+        </is>
+      </c>
+      <c r="AF80" t="inlineStr">
+        <is>
+          <t>77.78</t>
+        </is>
+      </c>
+      <c r="AG80" t="inlineStr">
+        <is>
+          <t>85.93</t>
+        </is>
+      </c>
+      <c r="AH80" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="AI80" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>-1.44</t>
+        </is>
+      </c>
+      <c r="AL80" t="inlineStr">
+        <is>
+          <t>20.48</t>
+        </is>
+      </c>
+      <c r="AM80" t="n">
+        <v>20.16</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>19.98</v>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>20.27</t>
+        </is>
+      </c>
+      <c r="AP80" t="inlineStr">
+        <is>
+          <t>38.09</t>
+        </is>
+      </c>
+      <c r="AQ80" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AR80" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AS80" t="inlineStr">
+        <is>
+          <t>0.79</t>
+        </is>
+      </c>
+      <c r="AT80" t="inlineStr">
+        <is>
+          <t>-83.86</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV80" t="inlineStr">
+        <is>
+          <t>29422182.78288543</t>
+        </is>
+      </c>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>12281215.0</t>
+        </is>
+      </c>
+      <c r="AX80" t="n">
+        <v>15176666.8</v>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>16864844.9</t>
+        </is>
+      </c>
+      <c r="AZ80" t="n">
+        <v>20327098.3</v>
+      </c>
+      <c r="BA80" t="inlineStr">
+        <is>
+          <t>-1688178</t>
+        </is>
+      </c>
+      <c r="BB80" t="inlineStr">
+        <is>
+          <t>-596869.5280007</t>
+        </is>
+      </c>
+      <c r="BC80" t="inlineStr">
+        <is>
+          <t>-777304.7251375262</t>
+        </is>
+      </c>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>12281215.0</t>
+        </is>
+      </c>
+      <c r="BE80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF80" t="inlineStr">
+        <is>
+          <t>20.45</t>
+        </is>
+      </c>
+      <c r="BG80" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="BH80" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="BI80" t="inlineStr">
+        <is>
+          <t>春源</t>
+        </is>
+      </c>
+      <c r="BJ80" t="inlineStr">
+        <is>
+          <t>春源</t>
+        </is>
+      </c>
+      <c r="BK80" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL80" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM80" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="BN80" t="inlineStr">
+        <is>
+          <t>1.166589855613648</t>
+        </is>
+      </c>
+      <c r="BO80" t="inlineStr">
+        <is>
+          <t>-1.196134907171803</t>
+        </is>
+      </c>
+      <c r="BP80" t="inlineStr">
+        <is>
+          <t>3.290941182656901</t>
+        </is>
+      </c>
+      <c r="BQ80" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR80" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS80" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
+      </c>
+      <c r="BT80" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="BU80" t="inlineStr">
+        <is>
+          <t>9.57</t>
+        </is>
+      </c>
+      <c r="BV80" t="inlineStr">
+        <is>
+          <t>9.3</t>
+        </is>
+      </c>
+      <c r="BW80" t="inlineStr">
+        <is>
+          <t>10.84%</t>
+        </is>
+      </c>
+      <c r="BX80" t="inlineStr">
+        <is>
+          <t>7.27%</t>
+        </is>
+      </c>
+      <c r="BY80" t="inlineStr">
+        <is>
+          <t>30.47</t>
+        </is>
+      </c>
+      <c r="BZ80" t="inlineStr">
+        <is>
+          <t>13374</t>
+        </is>
+      </c>
+      <c r="CA80" t="inlineStr">
+        <is>
+          <t>工程50.74%、鋼板35.82%、特殊鋼帶板4.32%、矽鋼材4.32%、特殊鋼材2.90%、倉儲設備1.15%、型鋼0.57%、加工業務0.18% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB80" t="inlineStr">
+        <is>
+          <t>春源-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC80" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右上上市</t>
+        </is>
+      </c>
+      <c r="CD80" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="CE80" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="CF80" t="inlineStr">
+        <is>
+          <t>20.25</t>
+        </is>
+      </c>
+      <c r="CG80" t="inlineStr">
+        <is>
+          <t>20.45</t>
+        </is>
+      </c>
+      <c r="CH80" t="inlineStr">
+        <is>
+          <t>19.04</t>
+        </is>
+      </c>
+      <c r="CI80" t="inlineStr">
+        <is>
+          <t>** 鋼鐵 - 冷熱軋鋼板捲、棒鋼盤元(捲狀條鋼)、冷熱軋不鏽鋼板捲、不鏽鋼棒線、裁剪加工、金屬製品、模具、建築工程** 建材營造 - 結構工程</t>
+        </is>
+      </c>
+      <c r="CJ80" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>【b1】</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>-0.49</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1107.513</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>20.45</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>-3.74</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>2025-07-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>2025-08-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>20.65</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>19.8</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>0.74</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>-2.36</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>23.16</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>-0.49</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr"/>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>1237</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>93.33</t>
+        </is>
+      </c>
+      <c r="AH81" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI81" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>0.91</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>-1.48</t>
+        </is>
+      </c>
+      <c r="AL81" t="inlineStr">
+        <is>
+          <t>20.46</t>
+        </is>
+      </c>
+      <c r="AM81" t="n">
+        <v>20.16</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>19.98</v>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>20.28</t>
+        </is>
+      </c>
+      <c r="AP81" t="inlineStr">
+        <is>
+          <t>51.97</t>
+        </is>
+      </c>
+      <c r="AQ81" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AR81" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AS81" t="inlineStr">
+        <is>
+          <t>0.79</t>
+        </is>
+      </c>
+      <c r="AT81" t="inlineStr">
+        <is>
+          <t>-85.40</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV81" t="inlineStr">
+        <is>
+          <t>29422182.78288543</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>22695242.0</t>
+        </is>
+      </c>
+      <c r="AX81" t="n">
+        <v>16860764.4</v>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>17515689.6</t>
+        </is>
+      </c>
+      <c r="AZ81" t="n">
+        <v>20384448.64</v>
+      </c>
+      <c r="BA81" t="inlineStr">
+        <is>
+          <t>-654925</t>
+        </is>
+      </c>
+      <c r="BB81" t="inlineStr">
+        <is>
+          <t>-564063.1285212772</t>
+        </is>
+      </c>
+      <c r="BC81" t="inlineStr">
+        <is>
+          <t>-442356.7308127098</t>
+        </is>
+      </c>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>22695242.0</t>
+        </is>
+      </c>
+      <c r="BE81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF81" t="inlineStr">
+        <is>
+          <t>20.45</t>
+        </is>
+      </c>
+      <c r="BG81" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="BH81" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="BI81" t="inlineStr">
+        <is>
+          <t>春源</t>
+        </is>
+      </c>
+      <c r="BJ81" t="inlineStr">
+        <is>
+          <t>春源</t>
+        </is>
+      </c>
+      <c r="BK81" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL81" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM81" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="BN81" t="inlineStr">
+        <is>
+          <t>1.166589855613648</t>
+        </is>
+      </c>
+      <c r="BO81" t="inlineStr">
+        <is>
+          <t>-1.196134907171803</t>
+        </is>
+      </c>
+      <c r="BP81" t="inlineStr">
+        <is>
+          <t>3.290941182656901</t>
+        </is>
+      </c>
+      <c r="BQ81" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR81" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS81" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
+      </c>
+      <c r="BT81" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="BU81" t="inlineStr">
+        <is>
+          <t>9.57</t>
+        </is>
+      </c>
+      <c r="BV81" t="inlineStr">
+        <is>
+          <t>9.3</t>
+        </is>
+      </c>
+      <c r="BW81" t="inlineStr">
+        <is>
+          <t>10.84%</t>
+        </is>
+      </c>
+      <c r="BX81" t="inlineStr">
+        <is>
+          <t>7.27%</t>
+        </is>
+      </c>
+      <c r="BY81" t="inlineStr">
+        <is>
+          <t>30.47</t>
+        </is>
+      </c>
+      <c r="BZ81" t="inlineStr">
+        <is>
+          <t>13374</t>
+        </is>
+      </c>
+      <c r="CA81" t="inlineStr">
+        <is>
+          <t>工程50.74%、鋼板35.82%、特殊鋼帶板4.32%、矽鋼材4.32%、特殊鋼材2.90%、倉儲設備1.15%、型鋼0.57%、加工業務0.18% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB81" t="inlineStr">
+        <is>
+          <t>春源-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC81" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右上上市</t>
+        </is>
+      </c>
+      <c r="CD81" t="inlineStr">
+        <is>
+          <t>20.55</t>
+        </is>
+      </c>
+      <c r="CE81" t="inlineStr">
+        <is>
+          <t>20.65</t>
+        </is>
+      </c>
+      <c r="CF81" t="inlineStr">
+        <is>
+          <t>20.35</t>
+        </is>
+      </c>
+      <c r="CG81" t="inlineStr">
+        <is>
+          <t>20.45</t>
+        </is>
+      </c>
+      <c r="CH81" t="inlineStr">
+        <is>
+          <t>19.04</t>
+        </is>
+      </c>
+      <c r="CI81" t="inlineStr">
+        <is>
+          <t>** 鋼鐵 - 冷熱軋鋼板捲、棒鋼盤元(捲狀條鋼)、冷熱軋不鏽鋼板捲、不鏽鋼棒線、裁剪加工、金屬製品、模具、建築工程** 建材營造 - 結構工程</t>
+        </is>
+      </c>
+      <c r="CJ81" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>【b1】</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>0.24</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>553.964</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>20.55</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>-3.85</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>2025-07-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>2025-08-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>20.65</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>19.8</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>-2.36</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>11.59</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr"/>
+      <c r="AD82" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AE82" t="inlineStr">
+        <is>
+          <t>1237</t>
+        </is>
+      </c>
+      <c r="AF82" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG82" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AH82" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AI82" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>0.72</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>-1.51</t>
+        </is>
+      </c>
+      <c r="AL82" t="inlineStr">
+        <is>
+          <t>20.45</t>
+        </is>
+      </c>
+      <c r="AM82" t="n">
+        <v>20.11</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>19.97</v>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>20.28</t>
+        </is>
+      </c>
+      <c r="AP82" t="inlineStr">
+        <is>
+          <t>71.17</t>
+        </is>
+      </c>
+      <c r="AQ82" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AR82" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AS82" t="inlineStr">
+        <is>
+          <t>0.79</t>
+        </is>
+      </c>
+      <c r="AT82" t="inlineStr">
+        <is>
+          <t>-87.30</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV82" t="inlineStr">
+        <is>
+          <t>29422182.78288543</t>
+        </is>
+      </c>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>11372791.0</t>
+        </is>
+      </c>
+      <c r="AX82" t="n">
+        <v>15635916.8</v>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>16262746.4</t>
+        </is>
+      </c>
+      <c r="AZ82" t="n">
+        <v>20133936.62</v>
+      </c>
+      <c r="BA82" t="inlineStr">
+        <is>
+          <t>-626829</t>
+        </is>
+      </c>
+      <c r="BB82" t="inlineStr">
+        <is>
+          <t>-586191.5644682895</t>
+        </is>
+      </c>
+      <c r="BC82" t="inlineStr">
+        <is>
+          <t>-1063849.748533946</t>
+        </is>
+      </c>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>11372791.0</t>
+        </is>
+      </c>
+      <c r="BE82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF82" t="inlineStr">
+        <is>
+          <t>20.45</t>
+        </is>
+      </c>
+      <c r="BG82" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="BH82" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="BI82" t="inlineStr">
+        <is>
+          <t>春源</t>
+        </is>
+      </c>
+      <c r="BJ82" t="inlineStr">
+        <is>
+          <t>春源</t>
+        </is>
+      </c>
+      <c r="BK82" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL82" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM82" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="BN82" t="inlineStr">
+        <is>
+          <t>1.166589855613648</t>
+        </is>
+      </c>
+      <c r="BO82" t="inlineStr">
+        <is>
+          <t>-1.196134907171803</t>
+        </is>
+      </c>
+      <c r="BP82" t="inlineStr">
+        <is>
+          <t>3.290941182656901</t>
+        </is>
+      </c>
+      <c r="BQ82" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR82" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS82" t="inlineStr">
+        <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="BT82" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="BU82" t="inlineStr">
+        <is>
+          <t>9.57</t>
+        </is>
+      </c>
+      <c r="BV82" t="inlineStr">
+        <is>
+          <t>9.3</t>
+        </is>
+      </c>
+      <c r="BW82" t="inlineStr">
+        <is>
+          <t>10.84%</t>
+        </is>
+      </c>
+      <c r="BX82" t="inlineStr">
+        <is>
+          <t>7.27%</t>
+        </is>
+      </c>
+      <c r="BY82" t="inlineStr">
+        <is>
+          <t>30.47</t>
+        </is>
+      </c>
+      <c r="BZ82" t="inlineStr">
+        <is>
+          <t>13374</t>
+        </is>
+      </c>
+      <c r="CA82" t="inlineStr">
+        <is>
+          <t>工程50.74%、鋼板35.82%、特殊鋼帶板4.32%、矽鋼材4.32%、特殊鋼材2.90%、倉儲設備1.15%、型鋼0.57%、加工業務0.18% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB82" t="inlineStr">
+        <is>
+          <t>春源-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC82" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右上上市</t>
+        </is>
+      </c>
+      <c r="CD82" t="inlineStr">
+        <is>
+          <t>20.6</t>
+        </is>
+      </c>
+      <c r="CE82" t="inlineStr">
+        <is>
+          <t>20.6</t>
+        </is>
+      </c>
+      <c r="CF82" t="inlineStr">
+        <is>
+          <t>20.45</t>
+        </is>
+      </c>
+      <c r="CG82" t="inlineStr">
+        <is>
+          <t>20.55</t>
+        </is>
+      </c>
+      <c r="CH82" t="inlineStr">
+        <is>
+          <t>19.04</t>
+        </is>
+      </c>
+      <c r="CI82" t="inlineStr">
+        <is>
+          <t>** 鋼鐵 - 冷熱軋鋼板捲、棒鋼盤元(捲狀條鋼)、冷熱軋不鏽鋼板捲、不鏽鋼棒線、裁剪加工、金屬製品、模具、建築工程** 建材營造 - 結構工程</t>
+        </is>
+      </c>
+      <c r="CJ82" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>【b1】</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>0.24</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>688.801</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>0.73</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>11.19</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>2025-07-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>2025-08-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>20.65</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>19.8</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>-2.36</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>14.41</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr"/>
+      <c r="AD83" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AE83" t="inlineStr">
+        <is>
+          <t>1237</t>
+        </is>
+      </c>
+      <c r="AF83" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG83" t="inlineStr">
+        <is>
+          <t>97.92</t>
+        </is>
+      </c>
+      <c r="AH83" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AI83" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>-1.52</t>
+        </is>
+      </c>
+      <c r="AL83" t="inlineStr">
+        <is>
+          <t>20.39</t>
+        </is>
+      </c>
+      <c r="AM83" t="n">
+        <v>20.05</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>19.96</v>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>20.27</t>
+        </is>
+      </c>
+      <c r="AP83" t="inlineStr">
+        <is>
+          <t>87.46</t>
+        </is>
+      </c>
+      <c r="AQ83" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AR83" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AS83" t="inlineStr">
+        <is>
+          <t>0.79</t>
+        </is>
+      </c>
+      <c r="AT83" t="inlineStr">
+        <is>
+          <t>-89.56</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV83" t="inlineStr">
+        <is>
+          <t>29422182.78288543</t>
+        </is>
+      </c>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>14110938.0</t>
+        </is>
+      </c>
+      <c r="AX83" t="n">
+        <v>18605284.4</v>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>16732192.2</t>
+        </is>
+      </c>
+      <c r="AZ83" t="n">
+        <v>20190650.78</v>
+      </c>
+      <c r="BA83" t="inlineStr">
+        <is>
+          <t>1873092</t>
+        </is>
+      </c>
+      <c r="BB83" t="inlineStr">
+        <is>
+          <t>-499344.6219108974</t>
+        </is>
+      </c>
+      <c r="BC83" t="inlineStr">
+        <is>
+          <t>-700582.5328309275</t>
+        </is>
+      </c>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>14110938.0</t>
+        </is>
+      </c>
+      <c r="BE83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF83" t="inlineStr">
+        <is>
+          <t>20.45</t>
+        </is>
+      </c>
+      <c r="BG83" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="BH83" t="inlineStr">
+        <is>
+          <t>0.24</t>
+        </is>
+      </c>
+      <c r="BI83" t="inlineStr">
+        <is>
+          <t>春源</t>
+        </is>
+      </c>
+      <c r="BJ83" t="inlineStr">
+        <is>
+          <t>春源</t>
+        </is>
+      </c>
+      <c r="BK83" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL83" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM83" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="BN83" t="inlineStr">
+        <is>
+          <t>1.166589855613648</t>
+        </is>
+      </c>
+      <c r="BO83" t="inlineStr">
+        <is>
+          <t>-1.196134907171803</t>
+        </is>
+      </c>
+      <c r="BP83" t="inlineStr">
+        <is>
+          <t>3.290941182656901</t>
+        </is>
+      </c>
+      <c r="BQ83" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR83" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS83" t="inlineStr">
+        <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="BT83" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="BU83" t="inlineStr">
+        <is>
+          <t>9.57</t>
+        </is>
+      </c>
+      <c r="BV83" t="inlineStr">
+        <is>
+          <t>9.3</t>
+        </is>
+      </c>
+      <c r="BW83" t="inlineStr">
+        <is>
+          <t>10.84%</t>
+        </is>
+      </c>
+      <c r="BX83" t="inlineStr">
+        <is>
+          <t>7.27%</t>
+        </is>
+      </c>
+      <c r="BY83" t="inlineStr">
+        <is>
+          <t>30.47</t>
+        </is>
+      </c>
+      <c r="BZ83" t="inlineStr">
+        <is>
+          <t>13374</t>
+        </is>
+      </c>
+      <c r="CA83" t="inlineStr">
+        <is>
+          <t>工程50.74%、鋼板35.82%、特殊鋼帶板4.32%、矽鋼材4.32%、特殊鋼材2.90%、倉儲設備1.15%、型鋼0.57%、加工業務0.18% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB83" t="inlineStr">
+        <is>
+          <t>春源-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC83" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右上上市</t>
+        </is>
+      </c>
+      <c r="CD83" t="inlineStr">
+        <is>
+          <t>20.45</t>
+        </is>
+      </c>
+      <c r="CE83" t="inlineStr">
+        <is>
+          <t>20.55</t>
+        </is>
+      </c>
+      <c r="CF83" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="CG83" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="CH83" t="inlineStr">
+        <is>
+          <t>19.04</t>
+        </is>
+      </c>
+      <c r="CI83" t="inlineStr">
+        <is>
+          <t>** 鋼鐵 - 冷熱軋鋼板捲、棒鋼盤元(捲狀條鋼)、冷熱軋不鏽鋼板捲、不鏽鋼棒線、裁剪加工、金屬製品、模具、建築工程** 建材營造 - 結構工程</t>
+        </is>
+      </c>
+      <c r="CJ83" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>【b1】</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>754.84</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>20.45</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>9.28</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>2025-07-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>2025-08-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>20.65</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>19.8</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>0.74</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>-2.36</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>15.79</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr"/>
+      <c r="AD84" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AE84" t="inlineStr">
+        <is>
+          <t>1237</t>
+        </is>
+      </c>
+      <c r="AF84" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG84" t="inlineStr">
+        <is>
+          <t>97.92</t>
+        </is>
+      </c>
+      <c r="AH84" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AI84" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>0.09</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>-1.53</t>
+        </is>
+      </c>
+      <c r="AL84" t="inlineStr">
+        <is>
+          <t>20.31</t>
+        </is>
+      </c>
+      <c r="AM84" t="n">
+        <v>19.98</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>19.96</v>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>20.27</t>
+        </is>
+      </c>
+      <c r="AP84" t="inlineStr">
+        <is>
+          <t>110.41</t>
+        </is>
+      </c>
+      <c r="AQ84" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AR84" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AS84" t="inlineStr">
+        <is>
+          <t>0.79</t>
+        </is>
+      </c>
+      <c r="AT84" t="inlineStr">
+        <is>
+          <t>-91.84</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV84" t="inlineStr">
+        <is>
+          <t>29422182.78288543</t>
+        </is>
+      </c>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>15423148.0</t>
+        </is>
+      </c>
+      <c r="AX84" t="n">
+        <v>19289641.2</v>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>17652100.2</t>
+        </is>
+      </c>
+      <c r="AZ84" t="n">
+        <v>20350387.22</v>
+      </c>
+      <c r="BA84" t="inlineStr">
+        <is>
+          <t>1637541</t>
+        </is>
+      </c>
+      <c r="BB84" t="inlineStr">
+        <is>
+          <t>-462755.9108345283</t>
+        </is>
+      </c>
+      <c r="BC84" t="inlineStr">
+        <is>
+          <t>-449981.4556540847</t>
+        </is>
+      </c>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>15423148.0</t>
+        </is>
+      </c>
+      <c r="BE84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF84" t="inlineStr">
+        <is>
+          <t>20.45</t>
+        </is>
+      </c>
+      <c r="BG84" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="BH84" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="BI84" t="inlineStr">
+        <is>
+          <t>春源</t>
+        </is>
+      </c>
+      <c r="BJ84" t="inlineStr">
+        <is>
+          <t>春源</t>
+        </is>
+      </c>
+      <c r="BK84" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL84" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM84" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="BN84" t="inlineStr">
+        <is>
+          <t>1.166589855613648</t>
+        </is>
+      </c>
+      <c r="BO84" t="inlineStr">
+        <is>
+          <t>-1.196134907171803</t>
+        </is>
+      </c>
+      <c r="BP84" t="inlineStr">
+        <is>
+          <t>3.290941182656901</t>
+        </is>
+      </c>
+      <c r="BQ84" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR84" t="inlineStr">
+        <is>
+          <t>價-量縮</t>
+        </is>
+      </c>
+      <c r="BS84" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
+      </c>
+      <c r="BT84" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="BU84" t="inlineStr">
+        <is>
+          <t>9.57</t>
+        </is>
+      </c>
+      <c r="BV84" t="inlineStr">
+        <is>
+          <t>9.3</t>
+        </is>
+      </c>
+      <c r="BW84" t="inlineStr">
+        <is>
+          <t>10.84%</t>
+        </is>
+      </c>
+      <c r="BX84" t="inlineStr">
+        <is>
+          <t>7.27%</t>
+        </is>
+      </c>
+      <c r="BY84" t="inlineStr">
+        <is>
+          <t>30.47</t>
+        </is>
+      </c>
+      <c r="BZ84" t="inlineStr">
+        <is>
+          <t>13374</t>
+        </is>
+      </c>
+      <c r="CA84" t="inlineStr">
+        <is>
+          <t>工程50.74%、鋼板35.82%、特殊鋼帶板4.32%、矽鋼材4.32%、特殊鋼材2.90%、倉儲設備1.15%、型鋼0.57%、加工業務0.18% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB84" t="inlineStr">
+        <is>
+          <t>春源-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC84" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右上上市</t>
+        </is>
+      </c>
+      <c r="CD84" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="CE84" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="CF84" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="CG84" t="inlineStr">
+        <is>
+          <t>20.45</t>
+        </is>
+      </c>
+      <c r="CH84" t="inlineStr">
+        <is>
+          <t>19.04</t>
+        </is>
+      </c>
+      <c r="CI84" t="inlineStr">
+        <is>
+          <t>** 鋼鐵 - 冷熱軋鋼板捲、棒鋼盤元(捲狀條鋼)、冷熱軋不鏽鋼板捲、不鏽鋼棒線、裁剪加工、金屬製品、模具、建築工程** 建材營造 - 結構工程</t>
+        </is>
+      </c>
+      <c r="CJ84" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>【d1】</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>-0.24</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>1019.978</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>20.35</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>2025-07-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>2025-08-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>20.65</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>19.8</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>-2.36</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>21.33</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr"/>
+      <c r="AD85" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AE85" t="inlineStr">
+        <is>
+          <t>1237</t>
+        </is>
+      </c>
+      <c r="AF85" t="inlineStr">
+        <is>
+          <t>93.75</t>
+        </is>
+      </c>
+      <c r="AG85" t="inlineStr">
+        <is>
+          <t>97.92</t>
+        </is>
+      </c>
+      <c r="AH85" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AI85" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>-0.22</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>-1.52</t>
+        </is>
+      </c>
+      <c r="AL85" t="inlineStr">
+        <is>
+          <t>20.23</t>
+        </is>
+      </c>
+      <c r="AM85" t="n">
+        <v>19.91</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>20.26</t>
+        </is>
+      </c>
+      <c r="AP85" t="inlineStr">
+        <is>
+          <t>145.22</t>
+        </is>
+      </c>
+      <c r="AQ85" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AR85" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AS85" t="inlineStr">
+        <is>
+          <t>0.79</t>
+        </is>
+      </c>
+      <c r="AT85" t="inlineStr">
+        <is>
+          <t>-94.09</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV85" t="inlineStr">
+        <is>
+          <t>29422182.78288543</t>
+        </is>
+      </c>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>20701703.0</t>
+        </is>
+      </c>
+      <c r="AX85" t="n">
+        <v>18553023</v>
+      </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t>18327514.0</t>
+        </is>
+      </c>
+      <c r="AZ85" t="n">
+        <v>20240377.18</v>
+      </c>
+      <c r="BA85" t="inlineStr">
+        <is>
+          <t>225509</t>
+        </is>
+      </c>
+      <c r="BB85" t="inlineStr">
+        <is>
+          <t>-465078.5390491545</t>
+        </is>
+      </c>
+      <c r="BC85" t="inlineStr">
+        <is>
+          <t>-216503.0791280903</t>
+        </is>
+      </c>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>20701703.0</t>
+        </is>
+      </c>
+      <c r="BE85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF85" t="inlineStr">
+        <is>
+          <t>20.45</t>
+        </is>
+      </c>
+      <c r="BG85" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="BH85" t="inlineStr">
+        <is>
+          <t>-0.49</t>
+        </is>
+      </c>
+      <c r="BI85" t="inlineStr">
+        <is>
+          <t>春源</t>
+        </is>
+      </c>
+      <c r="BJ85" t="inlineStr">
+        <is>
+          <t>春源</t>
+        </is>
+      </c>
+      <c r="BK85" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL85" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM85" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="BN85" t="inlineStr">
+        <is>
+          <t>1.166589855613648</t>
+        </is>
+      </c>
+      <c r="BO85" t="inlineStr">
+        <is>
+          <t>-1.196134907171803</t>
+        </is>
+      </c>
+      <c r="BP85" t="inlineStr">
+        <is>
+          <t>3.290941182656901</t>
+        </is>
+      </c>
+      <c r="BQ85" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR85" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS85" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
+      </c>
+      <c r="BT85" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="BU85" t="inlineStr">
+        <is>
+          <t>9.57</t>
+        </is>
+      </c>
+      <c r="BV85" t="inlineStr">
+        <is>
+          <t>9.3</t>
+        </is>
+      </c>
+      <c r="BW85" t="inlineStr">
+        <is>
+          <t>10.84%</t>
+        </is>
+      </c>
+      <c r="BX85" t="inlineStr">
+        <is>
+          <t>7.27%</t>
+        </is>
+      </c>
+      <c r="BY85" t="inlineStr">
+        <is>
+          <t>30.47</t>
+        </is>
+      </c>
+      <c r="BZ85" t="inlineStr">
+        <is>
+          <t>13374</t>
+        </is>
+      </c>
+      <c r="CA85" t="inlineStr">
+        <is>
+          <t>工程50.74%、鋼板35.82%、特殊鋼帶板4.32%、矽鋼材4.32%、特殊鋼材2.90%、倉儲設備1.15%、型鋼0.57%、加工業務0.18% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB85" t="inlineStr">
+        <is>
+          <t>春源-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC85" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右上上市</t>
+        </is>
+      </c>
+      <c r="CD85" t="inlineStr">
+        <is>
+          <t>20.45</t>
+        </is>
+      </c>
+      <c r="CE85" t="inlineStr">
+        <is>
+          <t>20.45</t>
+        </is>
+      </c>
+      <c r="CF85" t="inlineStr">
+        <is>
+          <t>20.2</t>
+        </is>
+      </c>
+      <c r="CG85" t="inlineStr">
+        <is>
+          <t>20.35</t>
+        </is>
+      </c>
+      <c r="CH85" t="inlineStr">
+        <is>
+          <t>19.04</t>
+        </is>
+      </c>
+      <c r="CI85" t="inlineStr">
+        <is>
+          <t>** 鋼鐵 - 冷熱軋鋼板捲、棒鋼盤元(捲狀條鋼)、冷熱軋不鏽鋼板捲、不鏽鋼棒線、裁剪加工、金屬製品、模具、建築工程** 建材營造 - 結構工程</t>
+        </is>
+      </c>
+      <c r="CJ85" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>【d1】</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>0.74</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>812.811</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>2025-07-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>2025-08-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>20.65</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>19.8</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>-2.36</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>17.00</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr"/>
+      <c r="AD86" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AE86" t="inlineStr">
+        <is>
+          <t>1237</t>
+        </is>
+      </c>
+      <c r="AF86" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG86" t="inlineStr">
+        <is>
+          <t>96.97</t>
+        </is>
+      </c>
+      <c r="AH86" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI86" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>-1.49</t>
+        </is>
+      </c>
+      <c r="AL86" t="inlineStr">
+        <is>
+          <t>20.12</t>
+        </is>
+      </c>
+      <c r="AM86" t="n">
+        <v>19.85</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>20.25</t>
+        </is>
+      </c>
+      <c r="AP86" t="inlineStr">
+        <is>
+          <t>222.51</t>
+        </is>
+      </c>
+      <c r="AQ86" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AR86" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AS86" t="inlineStr">
+        <is>
+          <t>0.79</t>
+        </is>
+      </c>
+      <c r="AT86" t="inlineStr">
+        <is>
+          <t>-96.24</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV86" t="inlineStr">
+        <is>
+          <t>29422182.78288543</t>
+        </is>
+      </c>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>16571004.0</t>
+        </is>
+      </c>
+      <c r="AX86" t="n">
+        <v>18170614.8</v>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t>17758365.3</t>
+        </is>
+      </c>
+      <c r="AZ86" t="n">
+        <v>20187873.48</v>
+      </c>
+      <c r="BA86" t="inlineStr">
+        <is>
+          <t>412249</t>
+        </is>
+      </c>
+      <c r="BB86" t="inlineStr">
+        <is>
+          <t>-510274.0772166207</t>
+        </is>
+      </c>
+      <c r="BC86" t="inlineStr">
+        <is>
+          <t>-440789.7526935264</t>
+        </is>
+      </c>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>16571004.0</t>
+        </is>
+      </c>
+      <c r="BE86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF86" t="inlineStr">
+        <is>
+          <t>20.45</t>
+        </is>
+      </c>
+      <c r="BG86" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="BH86" t="inlineStr">
+        <is>
+          <t>-0.24</t>
+        </is>
+      </c>
+      <c r="BI86" t="inlineStr">
+        <is>
+          <t>春源</t>
+        </is>
+      </c>
+      <c r="BJ86" t="inlineStr">
+        <is>
+          <t>春源</t>
+        </is>
+      </c>
+      <c r="BK86" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL86" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM86" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="BN86" t="inlineStr">
+        <is>
+          <t>1.166589855613648</t>
+        </is>
+      </c>
+      <c r="BO86" t="inlineStr">
+        <is>
+          <t>-1.196134907171803</t>
+        </is>
+      </c>
+      <c r="BP86" t="inlineStr">
+        <is>
+          <t>3.290941182656901</t>
+        </is>
+      </c>
+      <c r="BQ86" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BR86" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS86" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
+      </c>
+      <c r="BT86" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="BU86" t="inlineStr">
+        <is>
+          <t>9.57</t>
+        </is>
+      </c>
+      <c r="BV86" t="inlineStr">
+        <is>
+          <t>9.3</t>
+        </is>
+      </c>
+      <c r="BW86" t="inlineStr">
+        <is>
+          <t>10.84%</t>
+        </is>
+      </c>
+      <c r="BX86" t="inlineStr">
+        <is>
+          <t>7.27%</t>
+        </is>
+      </c>
+      <c r="BY86" t="inlineStr">
+        <is>
+          <t>30.47</t>
+        </is>
+      </c>
+      <c r="BZ86" t="inlineStr">
+        <is>
+          <t>13374</t>
+        </is>
+      </c>
+      <c r="CA86" t="inlineStr">
+        <is>
+          <t>工程50.74%、鋼板35.82%、特殊鋼帶板4.32%、矽鋼材4.32%、特殊鋼材2.90%、倉儲設備1.15%、型鋼0.57%、加工業務0.18% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB86" t="inlineStr">
+        <is>
+          <t>春源-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC86" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右上上市</t>
+        </is>
+      </c>
+      <c r="CD86" t="inlineStr">
+        <is>
+          <t>20.35</t>
+        </is>
+      </c>
+      <c r="CE86" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="CF86" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="CG86" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="CH86" t="inlineStr">
+        <is>
+          <t>19.04</t>
+        </is>
+      </c>
+      <c r="CI86" t="inlineStr">
+        <is>
+          <t>** 鋼鐵 - 冷熱軋鋼板捲、棒鋼盤元(捲狀條鋼)、冷熱軋不鏽鋼板捲、不鏽鋼棒線、裁剪加工、金屬製品、模具、建築工程** 建材營造 - 結構工程</t>
+        </is>
+      </c>
+      <c r="CJ86" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>【d1】</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>0.74</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>1293.122</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>20.25</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>-2.01</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>2025-07-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>2025-08-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>20.65</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>19.8</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>-2.36</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>27.05</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>-0.49</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr"/>
+      <c r="AD87" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AE87" t="inlineStr">
+        <is>
+          <t>1237</t>
+        </is>
+      </c>
+      <c r="AF87" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG87" t="inlineStr">
+        <is>
+          <t>88.64</t>
+        </is>
+      </c>
+      <c r="AH87" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI87" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>-0.8</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>-1.47</t>
+        </is>
+      </c>
+      <c r="AL87" t="inlineStr">
+        <is>
+          <t>20.02</t>
+        </is>
+      </c>
+      <c r="AM87" t="n">
+        <v>19.78</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>19.94</v>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>20.24</t>
+        </is>
+      </c>
+      <c r="AP87" t="inlineStr">
+        <is>
+          <t>398.09</t>
+        </is>
+      </c>
+      <c r="AQ87" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AR87" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AS87" t="inlineStr">
+        <is>
+          <t>0.79</t>
+        </is>
+      </c>
+      <c r="AT87" t="inlineStr">
+        <is>
+          <t>-98.33</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV87" t="inlineStr">
+        <is>
+          <t>29422182.78288543</t>
+        </is>
+      </c>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>26219629.0</t>
+        </is>
+      </c>
+      <c r="AX87" t="n">
+        <v>16889576</v>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>17236189.3</t>
+        </is>
+      </c>
+      <c r="AZ87" t="n">
+        <v>20277790.28</v>
+      </c>
+      <c r="BA87" t="inlineStr">
+        <is>
+          <t>-346613</t>
+        </is>
+      </c>
+      <c r="BB87" t="inlineStr">
+        <is>
+          <t>-522907.5907662741</t>
+        </is>
+      </c>
+      <c r="BC87" t="inlineStr">
+        <is>
+          <t>-302881.9023336619</t>
+        </is>
+      </c>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>26219629.0</t>
+        </is>
+      </c>
+      <c r="BE87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF87" t="inlineStr">
+        <is>
+          <t>20.45</t>
+        </is>
+      </c>
+      <c r="BG87" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="BH87" t="inlineStr">
+        <is>
+          <t>-0.98</t>
+        </is>
+      </c>
+      <c r="BI87" t="inlineStr">
+        <is>
+          <t>春源</t>
+        </is>
+      </c>
+      <c r="BJ87" t="inlineStr">
+        <is>
+          <t>春源</t>
+        </is>
+      </c>
+      <c r="BK87" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL87" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM87" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="BN87" t="inlineStr">
+        <is>
+          <t>1.166589855613648</t>
+        </is>
+      </c>
+      <c r="BO87" t="inlineStr">
+        <is>
+          <t>-1.196134907171803</t>
+        </is>
+      </c>
+      <c r="BP87" t="inlineStr">
+        <is>
+          <t>3.290941182656901</t>
+        </is>
+      </c>
+      <c r="BQ87" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BR87" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS87" t="inlineStr">
+        <is>
+          <t>1.06</t>
+        </is>
+      </c>
+      <c r="BT87" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="BU87" t="inlineStr">
+        <is>
+          <t>9.57</t>
+        </is>
+      </c>
+      <c r="BV87" t="inlineStr">
+        <is>
+          <t>9.3</t>
+        </is>
+      </c>
+      <c r="BW87" t="inlineStr">
+        <is>
+          <t>10.84%</t>
+        </is>
+      </c>
+      <c r="BX87" t="inlineStr">
+        <is>
+          <t>7.27%</t>
+        </is>
+      </c>
+      <c r="BY87" t="inlineStr">
+        <is>
+          <t>30.47</t>
+        </is>
+      </c>
+      <c r="BZ87" t="inlineStr">
+        <is>
+          <t>13374</t>
+        </is>
+      </c>
+      <c r="CA87" t="inlineStr">
+        <is>
+          <t>工程50.74%、鋼板35.82%、特殊鋼帶板4.32%、矽鋼材4.32%、特殊鋼材2.90%、倉儲設備1.15%、型鋼0.57%、加工業務0.18% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB87" t="inlineStr">
+        <is>
+          <t>春源-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC87" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右上上市</t>
+        </is>
+      </c>
+      <c r="CD87" t="inlineStr">
+        <is>
+          <t>20.2</t>
+        </is>
+      </c>
+      <c r="CE87" t="inlineStr">
+        <is>
+          <t>20.45</t>
+        </is>
+      </c>
+      <c r="CF87" t="inlineStr">
+        <is>
+          <t>20.15</t>
+        </is>
+      </c>
+      <c r="CG87" t="inlineStr">
+        <is>
+          <t>20.25</t>
+        </is>
+      </c>
+      <c r="CH87" t="inlineStr">
+        <is>
+          <t>19.04</t>
+        </is>
+      </c>
+      <c r="CI87" t="inlineStr">
+        <is>
+          <t>** 鋼鐵 - 冷熱軋鋼板捲、棒鋼盤元(捲狀條鋼)、冷熱軋不鏽鋼板捲、不鏽鋼棒線、裁剪加工、金屬製品、模具、建築工程** 建材營造 - 結構工程</t>
+        </is>
+      </c>
+      <c r="CJ87" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>【d1】</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>876.712</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>20.1</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>2.66</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>-10.71</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>2025-07-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>2025-08-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>20.65</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>19.8</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>-0.99</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>-2.36</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>18.34</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr"/>
+      <c r="AD88" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AE88" t="inlineStr">
+        <is>
+          <t>1237</t>
+        </is>
+      </c>
+      <c r="AF88" t="inlineStr">
+        <is>
+          <t>90.91</t>
+        </is>
+      </c>
+      <c r="AG88" t="inlineStr">
+        <is>
+          <t>66.41</t>
+        </is>
+      </c>
+      <c r="AH88" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AI88" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>-1.05</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>-1.46</t>
+        </is>
+      </c>
+      <c r="AL88" t="inlineStr">
+        <is>
+          <t>19.89</t>
+        </is>
+      </c>
+      <c r="AM88" t="n">
+        <v>19.73</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>19.94</v>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>20.24</t>
+        </is>
+      </c>
+      <c r="AP88" t="inlineStr">
+        <is>
+          <t>65587.40</t>
+        </is>
+      </c>
+      <c r="AQ88" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AR88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS88" t="inlineStr">
+        <is>
+          <t>0.79</t>
+        </is>
+      </c>
+      <c r="AT88" t="inlineStr">
+        <is>
+          <t>-99.99</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV88" t="inlineStr">
+        <is>
+          <t>29422182.78288543</t>
+        </is>
+      </c>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>17532722.0</t>
+        </is>
+      </c>
+      <c r="AX88" t="n">
+        <v>14859100</v>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>16642108.4</t>
+        </is>
+      </c>
+      <c r="AZ88" t="n">
+        <v>20371841.18</v>
+      </c>
+      <c r="BA88" t="inlineStr">
+        <is>
+          <t>-1783008</t>
+        </is>
+      </c>
+      <c r="BB88" t="inlineStr">
+        <is>
+          <t>-562912.2613903855</t>
+        </is>
+      </c>
+      <c r="BC88" t="inlineStr">
+        <is>
+          <t>-1128834.726736229</t>
+        </is>
+      </c>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>17532722.0</t>
+        </is>
+      </c>
+      <c r="BE88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF88" t="inlineStr">
+        <is>
+          <t>20.45</t>
+        </is>
+      </c>
+      <c r="BG88" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="BH88" t="inlineStr">
+        <is>
+          <t>-1.71</t>
+        </is>
+      </c>
+      <c r="BI88" t="inlineStr">
+        <is>
+          <t>春源</t>
+        </is>
+      </c>
+      <c r="BJ88" t="inlineStr">
+        <is>
+          <t>春源</t>
+        </is>
+      </c>
+      <c r="BK88" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL88" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM88" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="BN88" t="inlineStr">
+        <is>
+          <t>1.166589855613648</t>
+        </is>
+      </c>
+      <c r="BO88" t="inlineStr">
+        <is>
+          <t>-1.196134907171803</t>
+        </is>
+      </c>
+      <c r="BP88" t="inlineStr">
+        <is>
+          <t>3.290941182656901</t>
+        </is>
+      </c>
+      <c r="BQ88" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR88" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS88" t="inlineStr">
+        <is>
+          <t>1.06</t>
+        </is>
+      </c>
+      <c r="BT88" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="BU88" t="inlineStr">
+        <is>
+          <t>9.57</t>
+        </is>
+      </c>
+      <c r="BV88" t="inlineStr">
+        <is>
+          <t>9.3</t>
+        </is>
+      </c>
+      <c r="BW88" t="inlineStr">
+        <is>
+          <t>10.84%</t>
+        </is>
+      </c>
+      <c r="BX88" t="inlineStr">
+        <is>
+          <t>7.27%</t>
+        </is>
+      </c>
+      <c r="BY88" t="inlineStr">
+        <is>
+          <t>30.47</t>
+        </is>
+      </c>
+      <c r="BZ88" t="inlineStr">
+        <is>
+          <t>13374</t>
+        </is>
+      </c>
+      <c r="CA88" t="inlineStr">
+        <is>
+          <t>工程50.74%、鋼板35.82%、特殊鋼帶板4.32%、矽鋼材4.32%、特殊鋼材2.90%、倉儲設備1.15%、型鋼0.57%、加工業務0.18% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB88" t="inlineStr">
+        <is>
+          <t>春源-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC88" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右上上市</t>
+        </is>
+      </c>
+      <c r="CD88" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="CE88" t="inlineStr">
+        <is>
+          <t>20.15</t>
+        </is>
+      </c>
+      <c r="CF88" t="inlineStr">
+        <is>
+          <t>19.85</t>
+        </is>
+      </c>
+      <c r="CG88" t="inlineStr">
+        <is>
+          <t>20.1</t>
+        </is>
+      </c>
+      <c r="CH88" t="inlineStr">
+        <is>
+          <t>19.04</t>
+        </is>
+      </c>
+      <c r="CI88" t="inlineStr">
+        <is>
+          <t>** 鋼鐵 - 冷熱軋鋼板捲、棒鋼盤元(捲狀條鋼)、冷熱軋不鏽鋼板捲、不鏽鋼棒線、裁剪加工、金屬製品、模具、建築工程** 建材營造 - 結構工程</t>
+        </is>
+      </c>
+      <c r="CJ88" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>【d1】</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>587.867</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>20.05</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>2.91</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>-1.62</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>2025-07-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>2025-08-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>20.65</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>19.8</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>-1.23</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>-2.36</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>12.30</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr"/>
+      <c r="AD89" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AE89" t="inlineStr">
+        <is>
+          <t>1237</t>
+        </is>
+      </c>
+      <c r="AF89" t="inlineStr">
         <is>
           <t>75.0</t>
         </is>
       </c>
-      <c r="AG78" t="inlineStr">
+      <c r="AG89" t="inlineStr">
         <is>
           <t>52.78</t>
         </is>
       </c>
-      <c r="AH78" t="n">
+      <c r="AH89" t="n">
         <v>1.06</v>
       </c>
-      <c r="AI78" t="n">
+      <c r="AI89" t="n">
         <v>0.75</v>
       </c>
-      <c r="AJ78" t="inlineStr">
+      <c r="AJ89" t="inlineStr">
         <is>
           <t>-1.28</t>
         </is>
       </c>
-      <c r="AK78" t="inlineStr">
+      <c r="AK89" t="inlineStr">
         <is>
           <t>-1.41</t>
         </is>
       </c>
-      <c r="AL78" t="inlineStr">
+      <c r="AL89" t="inlineStr">
         <is>
           <t>19.84</t>
         </is>
       </c>
-      <c r="AM78" t="n">
+      <c r="AM89" t="n">
         <v>19.69</v>
       </c>
-      <c r="AN78" t="n">
+      <c r="AN89" t="n">
         <v>19.95</v>
       </c>
-      <c r="AO78" t="inlineStr">
+      <c r="AO89" t="inlineStr">
         <is>
           <t>20.23</t>
         </is>
       </c>
-      <c r="AP78" t="inlineStr">
+      <c r="AP89" t="inlineStr">
         <is>
           <t>343.93</t>
         </is>
       </c>
-      <c r="AQ78" t="n">
+      <c r="AQ89" t="n">
         <v>0.03</v>
       </c>
-      <c r="AR78" t="n">
+      <c r="AR89" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AS78" t="inlineStr">
+      <c r="AS89" t="inlineStr">
         <is>
           <t>0.79</t>
         </is>
       </c>
-      <c r="AT78" t="inlineStr">
+      <c r="AT89" t="inlineStr">
         <is>
           <t>-101.30</t>
         </is>
       </c>
-      <c r="AU78" t="inlineStr">
+      <c r="AU89" t="inlineStr">
         <is>
           <t>2025/11/06</t>
         </is>
       </c>
-      <c r="AV78" t="inlineStr">
+      <c r="AV89" t="inlineStr">
         <is>
           <t>29422182.78288543</t>
         </is>
       </c>
-      <c r="AW78" t="inlineStr">
+      <c r="AW89" t="inlineStr">
         <is>
           <t>11740057.0</t>
         </is>
       </c>
-      <c r="AX78" t="n">
+      <c r="AX89" t="n">
         <v>16014559.2</v>
       </c>
-      <c r="AY78" t="inlineStr">
+      <c r="AY89" t="inlineStr">
         <is>
           <t>16278001.2</t>
         </is>
       </c>
-      <c r="AZ78" t="n">
+      <c r="AZ89" t="n">
         <v>20292426.12</v>
       </c>
-      <c r="BA78" t="inlineStr">
+      <c r="BA89" t="inlineStr">
         <is>
           <t>-263442</t>
         </is>
       </c>
-      <c r="BB78" t="inlineStr">
+      <c r="BB89" t="inlineStr">
         <is>
           <t>-460017.2676911412</t>
         </is>
       </c>
-      <c r="BC78" t="inlineStr">
+      <c r="BC89" t="inlineStr">
         <is>
           <t>-1337711.771356456</t>
         </is>
       </c>
-      <c r="BD78" t="inlineStr">
+      <c r="BD89" t="inlineStr">
         <is>
           <t>11740057.0</t>
         </is>
       </c>
-      <c r="BE78" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF78" t="inlineStr">
+      <c r="BE89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF89" t="inlineStr">
         <is>
           <t>20.45</t>
         </is>
       </c>
-      <c r="BG78" t="inlineStr">
+      <c r="BG89" t="inlineStr">
         <is>
           <t>2025/12/01</t>
         </is>
       </c>
-      <c r="BH78" t="inlineStr">
+      <c r="BH89" t="inlineStr">
         <is>
           <t>-1.96</t>
         </is>
       </c>
-      <c r="BI78" t="inlineStr">
+      <c r="BI89" t="inlineStr">
         <is>
           <t>春源</t>
         </is>
       </c>
-      <c r="BJ78" t="inlineStr">
+      <c r="BJ89" t="inlineStr">
         <is>
           <t>春源</t>
         </is>
       </c>
-      <c r="BK78" t="inlineStr">
+      <c r="BK89" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BL78" t="inlineStr">
+      <c r="BL89" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BM78" t="inlineStr">
+      <c r="BM89" t="inlineStr">
         <is>
           <t>0.64</t>
         </is>
       </c>
-      <c r="BN78" t="inlineStr">
+      <c r="BN89" t="inlineStr">
         <is>
           <t>1.166589855613648</t>
         </is>
       </c>
-      <c r="BO78" t="inlineStr">
+      <c r="BO89" t="inlineStr">
         <is>
           <t>-1.196134907171803</t>
         </is>
       </c>
-      <c r="BP78" t="inlineStr">
+      <c r="BP89" t="inlineStr">
         <is>
           <t>3.290941182656901</t>
         </is>
       </c>
-      <c r="BQ78" t="inlineStr">
+      <c r="BQ89" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BR78" t="inlineStr">
+      <c r="BR89" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BS78" t="inlineStr">
+      <c r="BS89" t="inlineStr">
         <is>
           <t>1.05</t>
         </is>
       </c>
-      <c r="BT78" t="inlineStr">
+      <c r="BT89" t="inlineStr">
         <is>
           <t>6.3</t>
         </is>
       </c>
-      <c r="BU78" t="inlineStr">
+      <c r="BU89" t="inlineStr">
         <is>
           <t>9.57</t>
         </is>
       </c>
-      <c r="BV78" t="inlineStr">
+      <c r="BV89" t="inlineStr">
         <is>
           <t>9.3</t>
         </is>
       </c>
-      <c r="BW78" t="inlineStr">
+      <c r="BW89" t="inlineStr">
         <is>
           <t>10.84%</t>
         </is>
       </c>
-      <c r="BX78" t="inlineStr">
+      <c r="BX89" t="inlineStr">
         <is>
           <t>7.27%</t>
         </is>
       </c>
-      <c r="BY78" t="inlineStr">
+      <c r="BY89" t="inlineStr">
         <is>
           <t>30.47</t>
         </is>
       </c>
-      <c r="BZ78" t="inlineStr">
+      <c r="BZ89" t="inlineStr">
         <is>
           <t>13374</t>
         </is>
       </c>
-      <c r="CA78" t="inlineStr">
+      <c r="CA89" t="inlineStr">
         <is>
           <t>工程50.74%、鋼板35.82%、特殊鋼帶板4.32%、矽鋼材4.32%、特殊鋼材2.90%、倉儲設備1.15%、型鋼0.57%、加工業務0.18% (2024年)</t>
         </is>
       </c>
-      <c r="CB78" t="inlineStr">
+      <c r="CB89" t="inlineStr">
         <is>
           <t>春源-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CC78" t="inlineStr">
+      <c r="CC89" t="inlineStr">
         <is>
           <t>鋼鐵工業右上上市</t>
         </is>
       </c>
-      <c r="CD78" t="inlineStr">
+      <c r="CD89" t="inlineStr">
         <is>
           <t>19.9</t>
         </is>
       </c>
-      <c r="CE78" t="inlineStr">
+      <c r="CE89" t="inlineStr">
         <is>
           <t>20.05</t>
         </is>
       </c>
-      <c r="CF78" t="inlineStr">
+      <c r="CF89" t="inlineStr">
         <is>
           <t>19.85</t>
         </is>
       </c>
-      <c r="CG78" t="inlineStr">
+      <c r="CG89" t="inlineStr">
         <is>
           <t>20.05</t>
         </is>
       </c>
-      <c r="CH78" t="inlineStr">
+      <c r="CH89" t="inlineStr">
         <is>
           <t>19.04</t>
         </is>
       </c>
-      <c r="CI78" t="inlineStr">
+      <c r="CI89" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 冷熱軋鋼板捲、棒鋼盤元(捲狀條鋼)、冷熱軋不鏽鋼板捲、不鏽鋼棒線、裁剪加工、金屬製品、模具、建築工程** 建材營造 - 結構工程</t>
         </is>
       </c>
-      <c r="CJ78" t="inlineStr">
+      <c r="CJ89" t="inlineStr">
         <is>
           <t>False</t>
         </is>
